--- a/documents/Risk-Log.xlsx
+++ b/documents/Risk-Log.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Owner\Documents\cisc-699\final-project\documents\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F730898F-53B8-43B3-AC42-794183B1B8C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,9 +24,72 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+  <si>
+    <t>Risk number</t>
+  </si>
+  <si>
+    <t>Risk</t>
+  </si>
+  <si>
+    <t>Likelihood Score</t>
+  </si>
+  <si>
+    <t>Conseq Score</t>
+  </si>
+  <si>
+    <t>Risk Score</t>
+  </si>
+  <si>
+    <t>Net Score</t>
+  </si>
+  <si>
+    <t>Justification for the Likelihood score</t>
+  </si>
+  <si>
+    <t>Justification for the Consequence score</t>
+  </si>
+  <si>
+    <t>Mitigation (hardware and software)
+to bring the Risk down from Reds and Yellows to Low Green score</t>
+  </si>
+  <si>
+    <t>Q1 Behavior (Desired Behavior)</t>
+  </si>
+  <si>
+    <t>Q2 Behavior (Preventative Behavior)</t>
+  </si>
+  <si>
+    <t>Software Requirements Specs (SRS) for Q1 Behavior (Desired Behavior)</t>
+  </si>
+  <si>
+    <t>Software Requirements Specs (SRS) for Q2 Behavior (Preventative Behavior)</t>
+  </si>
+  <si>
+    <t>Test Cases for Q1 Behavior (Desired Behavior)</t>
+  </si>
+  <si>
+    <t>Test Cases for Q2 Behavior (Preventative Behavior)</t>
+  </si>
+  <si>
+    <t>Q3 Behavior
+(Responsive Behavior)</t>
+  </si>
+  <si>
+    <t>Software Requirements Specs (SRS) for Q3 Behavior
+(Responsive Behavior)</t>
+  </si>
+  <si>
+    <t>Test Cases for Q3 Behavior
+(Responsive Behavior)</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -28,16 +97,36 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,12 +134,33 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -330,10 +440,83 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:R1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.7109375" customWidth="1"/>
+    <col min="4" max="4" width="9.28515625" customWidth="1"/>
+    <col min="7" max="7" width="11.42578125" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
+    <col min="9" max="10" width="10.28515625" customWidth="1"/>
+    <col min="11" max="11" width="13.28515625" customWidth="1"/>
+    <col min="12" max="12" width="11.85546875" customWidth="1"/>
+    <col min="13" max="13" width="14.140625" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" customWidth="1"/>
+    <col min="16" max="16" width="14" customWidth="1"/>
+    <col min="17" max="17" width="13.140625" customWidth="1"/>
+    <col min="18" max="18" width="11.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:18" ht="195" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="R1" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/documents/Risk-Log.xlsx
+++ b/documents/Risk-Log.xlsx
@@ -8,24 +8,35 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Owner\Documents\cisc-699\final-project\documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F730898F-53B8-43B3-AC42-794183B1B8C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39FE5C44-1B89-4028-9AB6-F71ED2624104}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="59">
   <si>
     <t>Risk number</t>
   </si>
@@ -83,13 +94,136 @@
   <si>
     <t>Test Cases for Q3 Behavior
 (Responsive Behavior)</t>
+  </si>
+  <si>
+    <t>R1</t>
+  </si>
+  <si>
+    <t>Behind Schedule</t>
+  </si>
+  <si>
+    <t>This score was given due to having several vacations planned during the project where I would have limited access to technology</t>
+  </si>
+  <si>
+    <t>This score was given due to the nature of the project. A lot of the programs rely on previusly built programs/class. This means that a delay in the project sets the whole project back. With that said I also have lighter weeks in terms of school work that I can use to catch up.</t>
+  </si>
+  <si>
+    <t>All milestones and tasks to be completed by their assigned due date.</t>
+  </si>
+  <si>
+    <t>Working ahead on milestones when one is compleate.</t>
+  </si>
+  <si>
+    <t>Working tasks within a milestone to ensure they are completed by the milestone deadline and not there personal deadline</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>Checking Milestones-for-thesis file and seeing the green completed column up to the current date.</t>
+  </si>
+  <si>
+    <t>Checking Milestones-for-thesis file and seeing that no milestones are in red overdue</t>
+  </si>
+  <si>
+    <t>R2</t>
+  </si>
+  <si>
+    <t>Reprograming</t>
+  </si>
+  <si>
+    <t>4X3</t>
+  </si>
+  <si>
+    <t>5X4</t>
+  </si>
+  <si>
+    <t>This score was given due to having the big picture planned out but a lot of the implementation not planned.</t>
+  </si>
+  <si>
+    <t>A file that holds the milestones and associated due dates.</t>
+  </si>
+  <si>
+    <t>This score was given due to the flutuating scale of reprograming as a task. Most fixes are likely to be small code changes that should not effect the wider system.</t>
+  </si>
+  <si>
+    <t>Programs are split into proper modules to ensure that changes do not effect other systems.</t>
+  </si>
+  <si>
+    <t>Everything is programed with limited bugs</t>
+  </si>
+  <si>
+    <t>Programs are tested to ensure correctness</t>
+  </si>
+  <si>
+    <t>Checking Milestones-for-thesis file and seeing that tasks the next milestone are in progress or completed.</t>
+  </si>
+  <si>
+    <t>R3</t>
+  </si>
+  <si>
+    <t>R4</t>
+  </si>
+  <si>
+    <t>R5</t>
+  </si>
+  <si>
+    <t>Data Quality</t>
+  </si>
+  <si>
+    <t>This score was given due to the rushed nature of this project. However research done in previous classes should help validate data.</t>
+  </si>
+  <si>
+    <t>4X5</t>
+  </si>
+  <si>
+    <t>This score was given due to data being the main product of this project.If the data is of bad quality then there is not much reson for the project to exitst.</t>
+  </si>
+  <si>
+    <t>data validation using previous research</t>
+  </si>
+  <si>
+    <t>Class testing and black box testing to ensure correctness.</t>
+  </si>
+  <si>
+    <t>Poorly Defined Requirements</t>
+  </si>
+  <si>
+    <t>This score was given due to the project having very brifly defined requirements.</t>
+  </si>
+  <si>
+    <t>Software requirment document</t>
+  </si>
+  <si>
+    <t>This score was given due to the project having extreamly limited requirments that have left the project with out a true defanition of successful development.</t>
+  </si>
+  <si>
+    <t>Lack of Developers</t>
+  </si>
+  <si>
+    <t>3X3</t>
+  </si>
+  <si>
+    <t>This score was given due to the project being designed to be completed by one developer.</t>
+  </si>
+  <si>
+    <t>Comparing data outputs to datasets of observed predation studies.</t>
+  </si>
+  <si>
+    <t>Data matches observed patterns in the wild</t>
+  </si>
+  <si>
+    <t>Requirements are robust and meet the standards set by IEEE</t>
+  </si>
+  <si>
+    <t>Use IEEE guidelines to ensure requirements are formed correctly</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -101,6 +235,12 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -153,12 +293,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -441,23 +588,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R1"/>
+  <dimension ref="A1:R234"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.7109375" customWidth="1"/>
     <col min="4" max="4" width="9.28515625" customWidth="1"/>
-    <col min="7" max="7" width="11.42578125" customWidth="1"/>
-    <col min="8" max="8" width="12" customWidth="1"/>
-    <col min="9" max="10" width="10.28515625" customWidth="1"/>
-    <col min="11" max="11" width="13.28515625" customWidth="1"/>
-    <col min="12" max="12" width="11.85546875" customWidth="1"/>
-    <col min="13" max="13" width="14.140625" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" customWidth="1"/>
-    <col min="16" max="16" width="14" customWidth="1"/>
-    <col min="17" max="17" width="13.140625" customWidth="1"/>
-    <col min="18" max="18" width="11.7109375" customWidth="1"/>
+    <col min="7" max="7" width="37.7109375" customWidth="1"/>
+    <col min="8" max="8" width="41.7109375" customWidth="1"/>
+    <col min="9" max="9" width="35.5703125" customWidth="1"/>
+    <col min="10" max="10" width="16.5703125" customWidth="1"/>
+    <col min="11" max="11" width="17.28515625" customWidth="1"/>
+    <col min="12" max="12" width="16.85546875" customWidth="1"/>
+    <col min="13" max="13" width="22" customWidth="1"/>
+    <col min="14" max="14" width="24.28515625" customWidth="1"/>
+    <col min="15" max="15" width="26.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.5703125" customWidth="1"/>
+    <col min="17" max="17" width="21.85546875" customWidth="1"/>
+    <col min="18" max="18" width="19.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="195" x14ac:dyDescent="0.25">
@@ -516,7 +665,3485 @@
         <v>17</v>
       </c>
     </row>
+    <row r="2" spans="1:18" ht="135" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2">
+        <v>5</v>
+      </c>
+      <c r="D2">
+        <v>4</v>
+      </c>
+      <c r="E2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F2">
+        <f>C2*D2</f>
+        <v>20</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="L2" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="O2" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="R2" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" ht="105" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
+      <c r="D3">
+        <v>3</v>
+      </c>
+      <c r="E3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F3">
+        <f>C3*D3</f>
+        <v>12</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="L3" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="O3" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="P3" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q3" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="R3" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C4">
+        <v>4</v>
+      </c>
+      <c r="D4">
+        <v>5</v>
+      </c>
+      <c r="E4" t="s">
+        <v>44</v>
+      </c>
+      <c r="F4">
+        <f>C4*D4</f>
+        <v>20</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="N4" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="O4" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="P4" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q4" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="R4" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B5" t="s">
+        <v>48</v>
+      </c>
+      <c r="C5">
+        <v>4</v>
+      </c>
+      <c r="D5">
+        <v>5</v>
+      </c>
+      <c r="E5" t="s">
+        <v>44</v>
+      </c>
+      <c r="F5">
+        <f>C5*D5</f>
+        <v>20</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="N5" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="O5" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="P5" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q5" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="R5" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" ht="45" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C6">
+        <v>3</v>
+      </c>
+      <c r="D6">
+        <v>3</v>
+      </c>
+      <c r="E6" t="s">
+        <v>53</v>
+      </c>
+      <c r="F6" s="4">
+        <f>C6*D6</f>
+        <v>9</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="L6" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="M6" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="N6" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="O6" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="P6" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q6" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="R6" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3"/>
+      <c r="K7" s="3"/>
+      <c r="L7" s="3"/>
+      <c r="M7" s="3"/>
+      <c r="N7" s="3"/>
+      <c r="O7" s="3"/>
+      <c r="P7" s="3"/>
+      <c r="Q7" s="3"/>
+      <c r="R7" s="3"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="3"/>
+      <c r="J8" s="3"/>
+      <c r="K8" s="3"/>
+      <c r="L8" s="3"/>
+      <c r="M8" s="3"/>
+      <c r="N8" s="3"/>
+      <c r="O8" s="3"/>
+      <c r="P8" s="3"/>
+      <c r="Q8" s="3"/>
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3"/>
+      <c r="J9" s="3"/>
+      <c r="K9" s="3"/>
+      <c r="L9" s="3"/>
+      <c r="M9" s="3"/>
+      <c r="N9" s="3"/>
+      <c r="O9" s="3"/>
+      <c r="P9" s="3"/>
+      <c r="Q9" s="3"/>
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="G10" s="3"/>
+      <c r="H10" s="3"/>
+      <c r="I10" s="3"/>
+      <c r="J10" s="3"/>
+      <c r="K10" s="3"/>
+      <c r="L10" s="3"/>
+      <c r="M10" s="3"/>
+      <c r="N10" s="3"/>
+      <c r="O10" s="3"/>
+      <c r="P10" s="3"/>
+      <c r="Q10" s="3"/>
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="G11" s="3"/>
+      <c r="H11" s="3"/>
+      <c r="I11" s="3"/>
+      <c r="J11" s="3"/>
+      <c r="K11" s="3"/>
+      <c r="L11" s="3"/>
+      <c r="M11" s="3"/>
+      <c r="N11" s="3"/>
+      <c r="O11" s="3"/>
+      <c r="P11" s="3"/>
+      <c r="Q11" s="3"/>
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="G12" s="3"/>
+      <c r="H12" s="3"/>
+      <c r="I12" s="3"/>
+      <c r="J12" s="3"/>
+      <c r="K12" s="3"/>
+      <c r="L12" s="3"/>
+      <c r="M12" s="3"/>
+      <c r="N12" s="3"/>
+      <c r="O12" s="3"/>
+      <c r="P12" s="3"/>
+      <c r="Q12" s="3"/>
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="G13" s="3"/>
+      <c r="H13" s="3"/>
+      <c r="I13" s="3"/>
+      <c r="J13" s="3"/>
+      <c r="K13" s="3"/>
+      <c r="L13" s="3"/>
+      <c r="M13" s="3"/>
+      <c r="N13" s="3"/>
+      <c r="O13" s="3"/>
+      <c r="P13" s="3"/>
+      <c r="Q13" s="3"/>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="G14" s="3"/>
+      <c r="H14" s="3"/>
+      <c r="I14" s="3"/>
+      <c r="J14" s="3"/>
+      <c r="K14" s="3"/>
+      <c r="L14" s="3"/>
+      <c r="M14" s="3"/>
+      <c r="N14" s="3"/>
+      <c r="O14" s="3"/>
+      <c r="P14" s="3"/>
+      <c r="Q14" s="3"/>
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="G15" s="3"/>
+      <c r="H15" s="3"/>
+      <c r="I15" s="3"/>
+      <c r="J15" s="3"/>
+      <c r="K15" s="3"/>
+      <c r="L15" s="3"/>
+      <c r="M15" s="3"/>
+      <c r="N15" s="3"/>
+      <c r="O15" s="3"/>
+      <c r="P15" s="3"/>
+      <c r="Q15" s="3"/>
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="G16" s="3"/>
+      <c r="H16" s="3"/>
+      <c r="I16" s="3"/>
+      <c r="J16" s="3"/>
+      <c r="K16" s="3"/>
+      <c r="L16" s="3"/>
+      <c r="M16" s="3"/>
+      <c r="N16" s="3"/>
+      <c r="O16" s="3"/>
+      <c r="P16" s="3"/>
+      <c r="Q16" s="3"/>
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G17" s="3"/>
+      <c r="H17" s="3"/>
+      <c r="I17" s="3"/>
+      <c r="J17" s="3"/>
+      <c r="K17" s="3"/>
+      <c r="L17" s="3"/>
+      <c r="M17" s="3"/>
+      <c r="N17" s="3"/>
+      <c r="O17" s="3"/>
+      <c r="P17" s="3"/>
+      <c r="Q17" s="3"/>
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G18" s="3"/>
+      <c r="H18" s="3"/>
+      <c r="I18" s="3"/>
+      <c r="J18" s="3"/>
+      <c r="K18" s="3"/>
+      <c r="L18" s="3"/>
+      <c r="M18" s="3"/>
+      <c r="N18" s="3"/>
+      <c r="O18" s="3"/>
+      <c r="P18" s="3"/>
+      <c r="Q18" s="3"/>
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G19" s="3"/>
+      <c r="H19" s="3"/>
+      <c r="I19" s="3"/>
+      <c r="J19" s="3"/>
+      <c r="K19" s="3"/>
+      <c r="L19" s="3"/>
+      <c r="M19" s="3"/>
+      <c r="N19" s="3"/>
+      <c r="O19" s="3"/>
+      <c r="P19" s="3"/>
+      <c r="Q19" s="3"/>
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G20" s="3"/>
+      <c r="H20" s="3"/>
+      <c r="I20" s="3"/>
+      <c r="J20" s="3"/>
+      <c r="K20" s="3"/>
+      <c r="L20" s="3"/>
+      <c r="M20" s="3"/>
+      <c r="N20" s="3"/>
+      <c r="O20" s="3"/>
+      <c r="P20" s="3"/>
+      <c r="Q20" s="3"/>
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G21" s="3"/>
+      <c r="H21" s="3"/>
+      <c r="I21" s="3"/>
+      <c r="J21" s="3"/>
+      <c r="K21" s="3"/>
+      <c r="L21" s="3"/>
+      <c r="M21" s="3"/>
+      <c r="N21" s="3"/>
+      <c r="O21" s="3"/>
+      <c r="P21" s="3"/>
+      <c r="Q21" s="3"/>
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G22" s="3"/>
+      <c r="H22" s="3"/>
+      <c r="I22" s="3"/>
+      <c r="J22" s="3"/>
+      <c r="K22" s="3"/>
+      <c r="L22" s="3"/>
+      <c r="M22" s="3"/>
+      <c r="N22" s="3"/>
+      <c r="O22" s="3"/>
+      <c r="P22" s="3"/>
+      <c r="Q22" s="3"/>
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G23" s="3"/>
+      <c r="H23" s="3"/>
+      <c r="I23" s="3"/>
+      <c r="J23" s="3"/>
+      <c r="K23" s="3"/>
+      <c r="L23" s="3"/>
+      <c r="M23" s="3"/>
+      <c r="N23" s="3"/>
+      <c r="O23" s="3"/>
+      <c r="P23" s="3"/>
+      <c r="Q23" s="3"/>
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G24" s="3"/>
+      <c r="H24" s="3"/>
+      <c r="I24" s="3"/>
+      <c r="J24" s="3"/>
+      <c r="K24" s="3"/>
+      <c r="L24" s="3"/>
+      <c r="M24" s="3"/>
+      <c r="N24" s="3"/>
+      <c r="O24" s="3"/>
+      <c r="P24" s="3"/>
+      <c r="Q24" s="3"/>
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G25" s="3"/>
+      <c r="H25" s="3"/>
+      <c r="I25" s="3"/>
+      <c r="J25" s="3"/>
+      <c r="K25" s="3"/>
+      <c r="L25" s="3"/>
+      <c r="M25" s="3"/>
+      <c r="N25" s="3"/>
+      <c r="O25" s="3"/>
+      <c r="P25" s="3"/>
+      <c r="Q25" s="3"/>
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G26" s="3"/>
+      <c r="H26" s="3"/>
+      <c r="I26" s="3"/>
+      <c r="J26" s="3"/>
+      <c r="K26" s="3"/>
+      <c r="L26" s="3"/>
+      <c r="M26" s="3"/>
+      <c r="N26" s="3"/>
+      <c r="O26" s="3"/>
+      <c r="P26" s="3"/>
+      <c r="Q26" s="3"/>
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G27" s="3"/>
+      <c r="H27" s="3"/>
+      <c r="I27" s="3"/>
+      <c r="J27" s="3"/>
+      <c r="K27" s="3"/>
+      <c r="L27" s="3"/>
+      <c r="M27" s="3"/>
+      <c r="N27" s="3"/>
+      <c r="O27" s="3"/>
+      <c r="P27" s="3"/>
+      <c r="Q27" s="3"/>
+      <c r="R27" s="3"/>
+    </row>
+    <row r="28" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G28" s="3"/>
+      <c r="H28" s="3"/>
+      <c r="I28" s="3"/>
+      <c r="J28" s="3"/>
+      <c r="K28" s="3"/>
+      <c r="L28" s="3"/>
+      <c r="M28" s="3"/>
+      <c r="N28" s="3"/>
+      <c r="O28" s="3"/>
+      <c r="P28" s="3"/>
+      <c r="Q28" s="3"/>
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G29" s="3"/>
+      <c r="H29" s="3"/>
+      <c r="I29" s="3"/>
+      <c r="J29" s="3"/>
+      <c r="K29" s="3"/>
+      <c r="L29" s="3"/>
+      <c r="M29" s="3"/>
+      <c r="N29" s="3"/>
+      <c r="O29" s="3"/>
+      <c r="P29" s="3"/>
+      <c r="Q29" s="3"/>
+      <c r="R29" s="3"/>
+    </row>
+    <row r="30" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G30" s="3"/>
+      <c r="H30" s="3"/>
+      <c r="I30" s="3"/>
+      <c r="J30" s="3"/>
+      <c r="K30" s="3"/>
+      <c r="L30" s="3"/>
+      <c r="M30" s="3"/>
+      <c r="N30" s="3"/>
+      <c r="O30" s="3"/>
+      <c r="P30" s="3"/>
+      <c r="Q30" s="3"/>
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G31" s="3"/>
+      <c r="H31" s="3"/>
+      <c r="I31" s="3"/>
+      <c r="J31" s="3"/>
+      <c r="K31" s="3"/>
+      <c r="L31" s="3"/>
+      <c r="M31" s="3"/>
+      <c r="N31" s="3"/>
+      <c r="O31" s="3"/>
+      <c r="P31" s="3"/>
+      <c r="Q31" s="3"/>
+      <c r="R31" s="3"/>
+    </row>
+    <row r="32" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G32" s="3"/>
+      <c r="H32" s="3"/>
+      <c r="I32" s="3"/>
+      <c r="J32" s="3"/>
+      <c r="K32" s="3"/>
+      <c r="L32" s="3"/>
+      <c r="M32" s="3"/>
+      <c r="N32" s="3"/>
+      <c r="O32" s="3"/>
+      <c r="P32" s="3"/>
+      <c r="Q32" s="3"/>
+      <c r="R32" s="3"/>
+    </row>
+    <row r="33" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G33" s="3"/>
+      <c r="H33" s="3"/>
+      <c r="I33" s="3"/>
+      <c r="J33" s="3"/>
+      <c r="K33" s="3"/>
+      <c r="L33" s="3"/>
+      <c r="M33" s="3"/>
+      <c r="N33" s="3"/>
+      <c r="O33" s="3"/>
+      <c r="P33" s="3"/>
+      <c r="Q33" s="3"/>
+      <c r="R33" s="3"/>
+    </row>
+    <row r="34" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G34" s="3"/>
+      <c r="H34" s="3"/>
+      <c r="I34" s="3"/>
+      <c r="J34" s="3"/>
+      <c r="K34" s="3"/>
+      <c r="L34" s="3"/>
+      <c r="M34" s="3"/>
+      <c r="N34" s="3"/>
+      <c r="O34" s="3"/>
+      <c r="P34" s="3"/>
+      <c r="Q34" s="3"/>
+      <c r="R34" s="3"/>
+    </row>
+    <row r="35" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G35" s="3"/>
+      <c r="H35" s="3"/>
+      <c r="I35" s="3"/>
+      <c r="J35" s="3"/>
+      <c r="K35" s="3"/>
+      <c r="L35" s="3"/>
+      <c r="M35" s="3"/>
+      <c r="N35" s="3"/>
+      <c r="O35" s="3"/>
+      <c r="P35" s="3"/>
+      <c r="Q35" s="3"/>
+      <c r="R35" s="3"/>
+    </row>
+    <row r="36" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G36" s="3"/>
+      <c r="H36" s="3"/>
+      <c r="I36" s="3"/>
+      <c r="J36" s="3"/>
+      <c r="K36" s="3"/>
+      <c r="L36" s="3"/>
+      <c r="M36" s="3"/>
+      <c r="N36" s="3"/>
+      <c r="O36" s="3"/>
+      <c r="P36" s="3"/>
+      <c r="Q36" s="3"/>
+      <c r="R36" s="3"/>
+    </row>
+    <row r="37" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G37" s="3"/>
+      <c r="H37" s="3"/>
+      <c r="I37" s="3"/>
+      <c r="J37" s="3"/>
+      <c r="K37" s="3"/>
+      <c r="L37" s="3"/>
+      <c r="M37" s="3"/>
+      <c r="N37" s="3"/>
+      <c r="O37" s="3"/>
+      <c r="P37" s="3"/>
+      <c r="Q37" s="3"/>
+      <c r="R37" s="3"/>
+    </row>
+    <row r="38" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G38" s="3"/>
+      <c r="H38" s="3"/>
+      <c r="I38" s="3"/>
+      <c r="J38" s="3"/>
+      <c r="K38" s="3"/>
+      <c r="L38" s="3"/>
+      <c r="M38" s="3"/>
+      <c r="N38" s="3"/>
+      <c r="O38" s="3"/>
+      <c r="P38" s="3"/>
+      <c r="Q38" s="3"/>
+      <c r="R38" s="3"/>
+    </row>
+    <row r="39" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G39" s="3"/>
+      <c r="H39" s="3"/>
+      <c r="I39" s="3"/>
+      <c r="J39" s="3"/>
+      <c r="K39" s="3"/>
+      <c r="L39" s="3"/>
+      <c r="M39" s="3"/>
+      <c r="N39" s="3"/>
+      <c r="O39" s="3"/>
+      <c r="P39" s="3"/>
+      <c r="Q39" s="3"/>
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G40" s="3"/>
+      <c r="H40" s="3"/>
+      <c r="I40" s="3"/>
+      <c r="J40" s="3"/>
+      <c r="K40" s="3"/>
+      <c r="L40" s="3"/>
+      <c r="M40" s="3"/>
+      <c r="N40" s="3"/>
+      <c r="O40" s="3"/>
+      <c r="P40" s="3"/>
+      <c r="Q40" s="3"/>
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G41" s="3"/>
+      <c r="H41" s="3"/>
+      <c r="I41" s="3"/>
+      <c r="J41" s="3"/>
+      <c r="K41" s="3"/>
+      <c r="L41" s="3"/>
+      <c r="M41" s="3"/>
+      <c r="N41" s="3"/>
+      <c r="O41" s="3"/>
+      <c r="P41" s="3"/>
+      <c r="Q41" s="3"/>
+      <c r="R41" s="3"/>
+    </row>
+    <row r="42" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G42" s="3"/>
+      <c r="H42" s="3"/>
+      <c r="I42" s="3"/>
+      <c r="J42" s="3"/>
+      <c r="K42" s="3"/>
+      <c r="L42" s="3"/>
+      <c r="M42" s="3"/>
+      <c r="N42" s="3"/>
+      <c r="O42" s="3"/>
+      <c r="P42" s="3"/>
+      <c r="Q42" s="3"/>
+      <c r="R42" s="3"/>
+    </row>
+    <row r="43" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G43" s="3"/>
+      <c r="H43" s="3"/>
+      <c r="I43" s="3"/>
+      <c r="J43" s="3"/>
+      <c r="K43" s="3"/>
+      <c r="L43" s="3"/>
+      <c r="M43" s="3"/>
+      <c r="N43" s="3"/>
+      <c r="O43" s="3"/>
+      <c r="P43" s="3"/>
+      <c r="Q43" s="3"/>
+      <c r="R43" s="3"/>
+    </row>
+    <row r="44" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G44" s="3"/>
+      <c r="H44" s="3"/>
+      <c r="I44" s="3"/>
+      <c r="J44" s="3"/>
+      <c r="K44" s="3"/>
+      <c r="L44" s="3"/>
+      <c r="M44" s="3"/>
+      <c r="N44" s="3"/>
+      <c r="O44" s="3"/>
+      <c r="P44" s="3"/>
+      <c r="Q44" s="3"/>
+      <c r="R44" s="3"/>
+    </row>
+    <row r="45" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G45" s="3"/>
+      <c r="H45" s="3"/>
+      <c r="I45" s="3"/>
+      <c r="J45" s="3"/>
+      <c r="K45" s="3"/>
+      <c r="L45" s="3"/>
+      <c r="M45" s="3"/>
+      <c r="N45" s="3"/>
+      <c r="O45" s="3"/>
+      <c r="P45" s="3"/>
+      <c r="Q45" s="3"/>
+      <c r="R45" s="3"/>
+    </row>
+    <row r="46" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G46" s="3"/>
+      <c r="H46" s="3"/>
+      <c r="I46" s="3"/>
+      <c r="J46" s="3"/>
+      <c r="K46" s="3"/>
+      <c r="L46" s="3"/>
+      <c r="M46" s="3"/>
+      <c r="N46" s="3"/>
+      <c r="O46" s="3"/>
+      <c r="P46" s="3"/>
+      <c r="Q46" s="3"/>
+      <c r="R46" s="3"/>
+    </row>
+    <row r="47" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G47" s="3"/>
+      <c r="H47" s="3"/>
+      <c r="I47" s="3"/>
+      <c r="J47" s="3"/>
+      <c r="K47" s="3"/>
+      <c r="L47" s="3"/>
+      <c r="M47" s="3"/>
+      <c r="N47" s="3"/>
+      <c r="O47" s="3"/>
+      <c r="P47" s="3"/>
+      <c r="Q47" s="3"/>
+      <c r="R47" s="3"/>
+    </row>
+    <row r="48" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G48" s="3"/>
+      <c r="H48" s="3"/>
+      <c r="I48" s="3"/>
+      <c r="J48" s="3"/>
+      <c r="K48" s="3"/>
+      <c r="L48" s="3"/>
+      <c r="M48" s="3"/>
+      <c r="N48" s="3"/>
+      <c r="O48" s="3"/>
+      <c r="P48" s="3"/>
+      <c r="Q48" s="3"/>
+      <c r="R48" s="3"/>
+    </row>
+    <row r="49" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G49" s="3"/>
+      <c r="H49" s="3"/>
+      <c r="I49" s="3"/>
+      <c r="J49" s="3"/>
+      <c r="K49" s="3"/>
+      <c r="L49" s="3"/>
+      <c r="M49" s="3"/>
+      <c r="N49" s="3"/>
+      <c r="O49" s="3"/>
+      <c r="P49" s="3"/>
+      <c r="Q49" s="3"/>
+      <c r="R49" s="3"/>
+    </row>
+    <row r="50" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G50" s="3"/>
+      <c r="H50" s="3"/>
+      <c r="I50" s="3"/>
+      <c r="J50" s="3"/>
+      <c r="K50" s="3"/>
+      <c r="L50" s="3"/>
+      <c r="M50" s="3"/>
+      <c r="N50" s="3"/>
+      <c r="O50" s="3"/>
+      <c r="P50" s="3"/>
+      <c r="Q50" s="3"/>
+      <c r="R50" s="3"/>
+    </row>
+    <row r="51" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G51" s="3"/>
+      <c r="H51" s="3"/>
+      <c r="I51" s="3"/>
+      <c r="J51" s="3"/>
+      <c r="K51" s="3"/>
+      <c r="L51" s="3"/>
+      <c r="M51" s="3"/>
+      <c r="N51" s="3"/>
+      <c r="O51" s="3"/>
+      <c r="P51" s="3"/>
+      <c r="Q51" s="3"/>
+      <c r="R51" s="3"/>
+    </row>
+    <row r="52" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G52" s="3"/>
+      <c r="H52" s="3"/>
+      <c r="I52" s="3"/>
+      <c r="J52" s="3"/>
+      <c r="K52" s="3"/>
+      <c r="L52" s="3"/>
+      <c r="M52" s="3"/>
+      <c r="N52" s="3"/>
+      <c r="O52" s="3"/>
+      <c r="P52" s="3"/>
+      <c r="Q52" s="3"/>
+      <c r="R52" s="3"/>
+    </row>
+    <row r="53" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G53" s="3"/>
+      <c r="H53" s="3"/>
+      <c r="I53" s="3"/>
+      <c r="J53" s="3"/>
+      <c r="K53" s="3"/>
+      <c r="L53" s="3"/>
+      <c r="M53" s="3"/>
+      <c r="N53" s="3"/>
+      <c r="O53" s="3"/>
+      <c r="P53" s="3"/>
+      <c r="Q53" s="3"/>
+      <c r="R53" s="3"/>
+    </row>
+    <row r="54" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G54" s="3"/>
+      <c r="H54" s="3"/>
+      <c r="I54" s="3"/>
+      <c r="J54" s="3"/>
+      <c r="K54" s="3"/>
+      <c r="L54" s="3"/>
+      <c r="M54" s="3"/>
+      <c r="N54" s="3"/>
+      <c r="O54" s="3"/>
+      <c r="P54" s="3"/>
+      <c r="Q54" s="3"/>
+      <c r="R54" s="3"/>
+    </row>
+    <row r="55" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G55" s="3"/>
+      <c r="H55" s="3"/>
+      <c r="I55" s="3"/>
+      <c r="J55" s="3"/>
+      <c r="K55" s="3"/>
+      <c r="L55" s="3"/>
+      <c r="M55" s="3"/>
+      <c r="N55" s="3"/>
+      <c r="O55" s="3"/>
+      <c r="P55" s="3"/>
+      <c r="Q55" s="3"/>
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G56" s="3"/>
+      <c r="H56" s="3"/>
+      <c r="I56" s="3"/>
+      <c r="J56" s="3"/>
+      <c r="K56" s="3"/>
+      <c r="L56" s="3"/>
+      <c r="M56" s="3"/>
+      <c r="N56" s="3"/>
+      <c r="O56" s="3"/>
+      <c r="P56" s="3"/>
+      <c r="Q56" s="3"/>
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G57" s="3"/>
+      <c r="H57" s="3"/>
+      <c r="I57" s="3"/>
+      <c r="J57" s="3"/>
+      <c r="K57" s="3"/>
+      <c r="L57" s="3"/>
+      <c r="M57" s="3"/>
+      <c r="N57" s="3"/>
+      <c r="O57" s="3"/>
+      <c r="P57" s="3"/>
+      <c r="Q57" s="3"/>
+      <c r="R57" s="3"/>
+    </row>
+    <row r="58" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G58" s="3"/>
+      <c r="H58" s="3"/>
+      <c r="I58" s="3"/>
+      <c r="J58" s="3"/>
+      <c r="K58" s="3"/>
+      <c r="L58" s="3"/>
+      <c r="M58" s="3"/>
+      <c r="N58" s="3"/>
+      <c r="O58" s="3"/>
+      <c r="P58" s="3"/>
+      <c r="Q58" s="3"/>
+      <c r="R58" s="3"/>
+    </row>
+    <row r="59" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G59" s="3"/>
+      <c r="H59" s="3"/>
+      <c r="I59" s="3"/>
+      <c r="J59" s="3"/>
+      <c r="K59" s="3"/>
+      <c r="L59" s="3"/>
+      <c r="M59" s="3"/>
+      <c r="N59" s="3"/>
+      <c r="O59" s="3"/>
+      <c r="P59" s="3"/>
+      <c r="Q59" s="3"/>
+      <c r="R59" s="3"/>
+    </row>
+    <row r="60" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G60" s="3"/>
+      <c r="H60" s="3"/>
+      <c r="I60" s="3"/>
+      <c r="J60" s="3"/>
+      <c r="K60" s="3"/>
+      <c r="L60" s="3"/>
+      <c r="M60" s="3"/>
+      <c r="N60" s="3"/>
+      <c r="O60" s="3"/>
+      <c r="P60" s="3"/>
+      <c r="Q60" s="3"/>
+      <c r="R60" s="3"/>
+    </row>
+    <row r="61" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G61" s="3"/>
+      <c r="H61" s="3"/>
+      <c r="I61" s="3"/>
+      <c r="J61" s="3"/>
+      <c r="K61" s="3"/>
+      <c r="L61" s="3"/>
+      <c r="M61" s="3"/>
+      <c r="N61" s="3"/>
+      <c r="O61" s="3"/>
+      <c r="P61" s="3"/>
+      <c r="Q61" s="3"/>
+      <c r="R61" s="3"/>
+    </row>
+    <row r="62" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G62" s="3"/>
+      <c r="H62" s="3"/>
+      <c r="I62" s="3"/>
+      <c r="J62" s="3"/>
+      <c r="K62" s="3"/>
+      <c r="L62" s="3"/>
+      <c r="M62" s="3"/>
+      <c r="N62" s="3"/>
+      <c r="O62" s="3"/>
+      <c r="P62" s="3"/>
+      <c r="Q62" s="3"/>
+      <c r="R62" s="3"/>
+    </row>
+    <row r="63" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G63" s="3"/>
+      <c r="H63" s="3"/>
+      <c r="I63" s="3"/>
+      <c r="J63" s="3"/>
+      <c r="K63" s="3"/>
+      <c r="L63" s="3"/>
+      <c r="M63" s="3"/>
+      <c r="N63" s="3"/>
+      <c r="O63" s="3"/>
+      <c r="P63" s="3"/>
+      <c r="Q63" s="3"/>
+      <c r="R63" s="3"/>
+    </row>
+    <row r="64" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G64" s="3"/>
+      <c r="H64" s="3"/>
+      <c r="I64" s="3"/>
+      <c r="J64" s="3"/>
+      <c r="K64" s="3"/>
+      <c r="L64" s="3"/>
+      <c r="M64" s="3"/>
+      <c r="N64" s="3"/>
+      <c r="O64" s="3"/>
+      <c r="P64" s="3"/>
+      <c r="Q64" s="3"/>
+      <c r="R64" s="3"/>
+    </row>
+    <row r="65" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G65" s="3"/>
+      <c r="H65" s="3"/>
+      <c r="I65" s="3"/>
+      <c r="J65" s="3"/>
+      <c r="K65" s="3"/>
+      <c r="L65" s="3"/>
+      <c r="M65" s="3"/>
+      <c r="N65" s="3"/>
+      <c r="O65" s="3"/>
+      <c r="P65" s="3"/>
+      <c r="Q65" s="3"/>
+      <c r="R65" s="3"/>
+    </row>
+    <row r="66" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G66" s="3"/>
+      <c r="H66" s="3"/>
+      <c r="I66" s="3"/>
+      <c r="J66" s="3"/>
+      <c r="K66" s="3"/>
+      <c r="L66" s="3"/>
+      <c r="M66" s="3"/>
+      <c r="N66" s="3"/>
+      <c r="O66" s="3"/>
+      <c r="P66" s="3"/>
+      <c r="Q66" s="3"/>
+      <c r="R66" s="3"/>
+    </row>
+    <row r="67" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G67" s="3"/>
+      <c r="H67" s="3"/>
+      <c r="I67" s="3"/>
+      <c r="J67" s="3"/>
+      <c r="K67" s="3"/>
+      <c r="L67" s="3"/>
+      <c r="M67" s="3"/>
+      <c r="N67" s="3"/>
+      <c r="O67" s="3"/>
+      <c r="P67" s="3"/>
+      <c r="Q67" s="3"/>
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G68" s="3"/>
+      <c r="H68" s="3"/>
+      <c r="I68" s="3"/>
+      <c r="J68" s="3"/>
+      <c r="K68" s="3"/>
+      <c r="L68" s="3"/>
+      <c r="M68" s="3"/>
+      <c r="N68" s="3"/>
+      <c r="O68" s="3"/>
+      <c r="P68" s="3"/>
+      <c r="Q68" s="3"/>
+      <c r="R68" s="3"/>
+    </row>
+    <row r="69" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G69" s="3"/>
+      <c r="H69" s="3"/>
+      <c r="I69" s="3"/>
+      <c r="J69" s="3"/>
+      <c r="K69" s="3"/>
+      <c r="L69" s="3"/>
+      <c r="M69" s="3"/>
+      <c r="N69" s="3"/>
+      <c r="O69" s="3"/>
+      <c r="P69" s="3"/>
+      <c r="Q69" s="3"/>
+      <c r="R69" s="3"/>
+    </row>
+    <row r="70" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G70" s="3"/>
+      <c r="H70" s="3"/>
+      <c r="I70" s="3"/>
+      <c r="J70" s="3"/>
+      <c r="K70" s="3"/>
+      <c r="L70" s="3"/>
+      <c r="M70" s="3"/>
+      <c r="N70" s="3"/>
+      <c r="O70" s="3"/>
+      <c r="P70" s="3"/>
+      <c r="Q70" s="3"/>
+      <c r="R70" s="3"/>
+    </row>
+    <row r="71" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G71" s="3"/>
+      <c r="H71" s="3"/>
+      <c r="I71" s="3"/>
+      <c r="J71" s="3"/>
+      <c r="K71" s="3"/>
+      <c r="L71" s="3"/>
+      <c r="M71" s="3"/>
+      <c r="N71" s="3"/>
+      <c r="O71" s="3"/>
+      <c r="P71" s="3"/>
+      <c r="Q71" s="3"/>
+      <c r="R71" s="3"/>
+    </row>
+    <row r="72" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G72" s="3"/>
+      <c r="H72" s="3"/>
+      <c r="I72" s="3"/>
+      <c r="J72" s="3"/>
+      <c r="K72" s="3"/>
+      <c r="L72" s="3"/>
+      <c r="M72" s="3"/>
+      <c r="N72" s="3"/>
+      <c r="O72" s="3"/>
+      <c r="P72" s="3"/>
+      <c r="Q72" s="3"/>
+      <c r="R72" s="3"/>
+    </row>
+    <row r="73" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G73" s="3"/>
+      <c r="H73" s="3"/>
+      <c r="I73" s="3"/>
+      <c r="J73" s="3"/>
+      <c r="K73" s="3"/>
+      <c r="L73" s="3"/>
+      <c r="M73" s="3"/>
+      <c r="N73" s="3"/>
+      <c r="O73" s="3"/>
+      <c r="P73" s="3"/>
+      <c r="Q73" s="3"/>
+      <c r="R73" s="3"/>
+    </row>
+    <row r="74" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G74" s="3"/>
+      <c r="H74" s="3"/>
+      <c r="I74" s="3"/>
+      <c r="J74" s="3"/>
+      <c r="K74" s="3"/>
+      <c r="L74" s="3"/>
+      <c r="M74" s="3"/>
+      <c r="N74" s="3"/>
+      <c r="O74" s="3"/>
+      <c r="P74" s="3"/>
+      <c r="Q74" s="3"/>
+      <c r="R74" s="3"/>
+    </row>
+    <row r="75" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G75" s="3"/>
+      <c r="H75" s="3"/>
+      <c r="I75" s="3"/>
+      <c r="J75" s="3"/>
+      <c r="K75" s="3"/>
+      <c r="L75" s="3"/>
+      <c r="M75" s="3"/>
+      <c r="N75" s="3"/>
+      <c r="O75" s="3"/>
+      <c r="P75" s="3"/>
+      <c r="Q75" s="3"/>
+      <c r="R75" s="3"/>
+    </row>
+    <row r="76" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G76" s="3"/>
+      <c r="H76" s="3"/>
+      <c r="I76" s="3"/>
+      <c r="J76" s="3"/>
+      <c r="K76" s="3"/>
+      <c r="L76" s="3"/>
+      <c r="M76" s="3"/>
+      <c r="N76" s="3"/>
+      <c r="O76" s="3"/>
+      <c r="P76" s="3"/>
+      <c r="Q76" s="3"/>
+      <c r="R76" s="3"/>
+    </row>
+    <row r="77" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G77" s="3"/>
+      <c r="H77" s="3"/>
+      <c r="I77" s="3"/>
+      <c r="J77" s="3"/>
+      <c r="K77" s="3"/>
+      <c r="L77" s="3"/>
+      <c r="M77" s="3"/>
+      <c r="N77" s="3"/>
+      <c r="O77" s="3"/>
+      <c r="P77" s="3"/>
+      <c r="Q77" s="3"/>
+      <c r="R77" s="3"/>
+    </row>
+    <row r="78" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G78" s="3"/>
+      <c r="H78" s="3"/>
+      <c r="I78" s="3"/>
+      <c r="J78" s="3"/>
+      <c r="K78" s="3"/>
+      <c r="L78" s="3"/>
+      <c r="M78" s="3"/>
+      <c r="N78" s="3"/>
+      <c r="O78" s="3"/>
+      <c r="P78" s="3"/>
+      <c r="Q78" s="3"/>
+      <c r="R78" s="3"/>
+    </row>
+    <row r="79" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G79" s="3"/>
+      <c r="H79" s="3"/>
+      <c r="I79" s="3"/>
+      <c r="J79" s="3"/>
+      <c r="K79" s="3"/>
+      <c r="L79" s="3"/>
+      <c r="M79" s="3"/>
+      <c r="N79" s="3"/>
+      <c r="O79" s="3"/>
+      <c r="P79" s="3"/>
+      <c r="Q79" s="3"/>
+      <c r="R79" s="3"/>
+    </row>
+    <row r="80" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G80" s="3"/>
+      <c r="H80" s="3"/>
+      <c r="I80" s="3"/>
+      <c r="J80" s="3"/>
+      <c r="K80" s="3"/>
+      <c r="L80" s="3"/>
+      <c r="M80" s="3"/>
+      <c r="N80" s="3"/>
+      <c r="O80" s="3"/>
+      <c r="P80" s="3"/>
+      <c r="Q80" s="3"/>
+      <c r="R80" s="3"/>
+    </row>
+    <row r="81" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G81" s="3"/>
+      <c r="H81" s="3"/>
+      <c r="I81" s="3"/>
+      <c r="J81" s="3"/>
+      <c r="K81" s="3"/>
+      <c r="L81" s="3"/>
+      <c r="M81" s="3"/>
+      <c r="N81" s="3"/>
+      <c r="O81" s="3"/>
+      <c r="P81" s="3"/>
+      <c r="Q81" s="3"/>
+      <c r="R81" s="3"/>
+    </row>
+    <row r="82" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G82" s="3"/>
+      <c r="H82" s="3"/>
+      <c r="I82" s="3"/>
+      <c r="J82" s="3"/>
+      <c r="K82" s="3"/>
+      <c r="L82" s="3"/>
+      <c r="M82" s="3"/>
+      <c r="N82" s="3"/>
+      <c r="O82" s="3"/>
+      <c r="P82" s="3"/>
+      <c r="Q82" s="3"/>
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G83" s="3"/>
+      <c r="H83" s="3"/>
+      <c r="I83" s="3"/>
+      <c r="J83" s="3"/>
+      <c r="K83" s="3"/>
+      <c r="L83" s="3"/>
+      <c r="M83" s="3"/>
+      <c r="N83" s="3"/>
+      <c r="O83" s="3"/>
+      <c r="P83" s="3"/>
+      <c r="Q83" s="3"/>
+      <c r="R83" s="3"/>
+    </row>
+    <row r="84" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G84" s="3"/>
+      <c r="H84" s="3"/>
+      <c r="I84" s="3"/>
+      <c r="J84" s="3"/>
+      <c r="K84" s="3"/>
+      <c r="L84" s="3"/>
+      <c r="M84" s="3"/>
+      <c r="N84" s="3"/>
+      <c r="O84" s="3"/>
+      <c r="P84" s="3"/>
+      <c r="Q84" s="3"/>
+      <c r="R84" s="3"/>
+    </row>
+    <row r="85" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G85" s="3"/>
+      <c r="H85" s="3"/>
+      <c r="I85" s="3"/>
+      <c r="J85" s="3"/>
+      <c r="K85" s="3"/>
+      <c r="L85" s="3"/>
+      <c r="M85" s="3"/>
+      <c r="N85" s="3"/>
+      <c r="O85" s="3"/>
+      <c r="P85" s="3"/>
+      <c r="Q85" s="3"/>
+      <c r="R85" s="3"/>
+    </row>
+    <row r="86" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G86" s="3"/>
+      <c r="H86" s="3"/>
+      <c r="I86" s="3"/>
+      <c r="J86" s="3"/>
+      <c r="K86" s="3"/>
+      <c r="L86" s="3"/>
+      <c r="M86" s="3"/>
+      <c r="N86" s="3"/>
+      <c r="O86" s="3"/>
+      <c r="P86" s="3"/>
+      <c r="Q86" s="3"/>
+      <c r="R86" s="3"/>
+    </row>
+    <row r="87" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G87" s="3"/>
+      <c r="H87" s="3"/>
+      <c r="I87" s="3"/>
+      <c r="J87" s="3"/>
+      <c r="K87" s="3"/>
+      <c r="L87" s="3"/>
+      <c r="M87" s="3"/>
+      <c r="N87" s="3"/>
+      <c r="O87" s="3"/>
+      <c r="P87" s="3"/>
+      <c r="Q87" s="3"/>
+      <c r="R87" s="3"/>
+    </row>
+    <row r="88" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G88" s="3"/>
+      <c r="H88" s="3"/>
+      <c r="I88" s="3"/>
+      <c r="J88" s="3"/>
+      <c r="K88" s="3"/>
+      <c r="L88" s="3"/>
+      <c r="M88" s="3"/>
+      <c r="N88" s="3"/>
+      <c r="O88" s="3"/>
+      <c r="P88" s="3"/>
+      <c r="Q88" s="3"/>
+      <c r="R88" s="3"/>
+    </row>
+    <row r="89" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G89" s="3"/>
+      <c r="H89" s="3"/>
+      <c r="I89" s="3"/>
+      <c r="J89" s="3"/>
+      <c r="K89" s="3"/>
+      <c r="L89" s="3"/>
+      <c r="M89" s="3"/>
+      <c r="N89" s="3"/>
+      <c r="O89" s="3"/>
+      <c r="P89" s="3"/>
+      <c r="Q89" s="3"/>
+      <c r="R89" s="3"/>
+    </row>
+    <row r="90" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G90" s="3"/>
+      <c r="H90" s="3"/>
+      <c r="I90" s="3"/>
+      <c r="J90" s="3"/>
+      <c r="K90" s="3"/>
+      <c r="L90" s="3"/>
+      <c r="M90" s="3"/>
+      <c r="N90" s="3"/>
+      <c r="O90" s="3"/>
+      <c r="P90" s="3"/>
+      <c r="Q90" s="3"/>
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G91" s="3"/>
+      <c r="H91" s="3"/>
+      <c r="I91" s="3"/>
+      <c r="J91" s="3"/>
+      <c r="K91" s="3"/>
+      <c r="L91" s="3"/>
+      <c r="M91" s="3"/>
+      <c r="N91" s="3"/>
+      <c r="O91" s="3"/>
+      <c r="P91" s="3"/>
+      <c r="Q91" s="3"/>
+      <c r="R91" s="3"/>
+    </row>
+    <row r="92" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G92" s="3"/>
+      <c r="H92" s="3"/>
+      <c r="I92" s="3"/>
+      <c r="J92" s="3"/>
+      <c r="K92" s="3"/>
+      <c r="L92" s="3"/>
+      <c r="M92" s="3"/>
+      <c r="N92" s="3"/>
+      <c r="O92" s="3"/>
+      <c r="P92" s="3"/>
+      <c r="Q92" s="3"/>
+      <c r="R92" s="3"/>
+    </row>
+    <row r="93" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G93" s="3"/>
+      <c r="H93" s="3"/>
+      <c r="I93" s="3"/>
+      <c r="J93" s="3"/>
+      <c r="K93" s="3"/>
+      <c r="L93" s="3"/>
+      <c r="M93" s="3"/>
+      <c r="N93" s="3"/>
+      <c r="O93" s="3"/>
+      <c r="P93" s="3"/>
+      <c r="Q93" s="3"/>
+      <c r="R93" s="3"/>
+    </row>
+    <row r="94" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G94" s="3"/>
+      <c r="H94" s="3"/>
+      <c r="I94" s="3"/>
+      <c r="J94" s="3"/>
+      <c r="K94" s="3"/>
+      <c r="L94" s="3"/>
+      <c r="M94" s="3"/>
+      <c r="N94" s="3"/>
+      <c r="O94" s="3"/>
+      <c r="P94" s="3"/>
+      <c r="Q94" s="3"/>
+      <c r="R94" s="3"/>
+    </row>
+    <row r="95" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G95" s="3"/>
+      <c r="H95" s="3"/>
+      <c r="I95" s="3"/>
+      <c r="J95" s="3"/>
+      <c r="K95" s="3"/>
+      <c r="L95" s="3"/>
+      <c r="M95" s="3"/>
+      <c r="N95" s="3"/>
+      <c r="O95" s="3"/>
+      <c r="P95" s="3"/>
+      <c r="Q95" s="3"/>
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G96" s="3"/>
+      <c r="H96" s="3"/>
+      <c r="I96" s="3"/>
+      <c r="J96" s="3"/>
+      <c r="K96" s="3"/>
+      <c r="L96" s="3"/>
+      <c r="M96" s="3"/>
+      <c r="N96" s="3"/>
+      <c r="O96" s="3"/>
+      <c r="P96" s="3"/>
+      <c r="Q96" s="3"/>
+      <c r="R96" s="3"/>
+    </row>
+    <row r="97" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G97" s="3"/>
+      <c r="H97" s="3"/>
+      <c r="I97" s="3"/>
+      <c r="J97" s="3"/>
+      <c r="K97" s="3"/>
+      <c r="L97" s="3"/>
+      <c r="M97" s="3"/>
+      <c r="N97" s="3"/>
+      <c r="O97" s="3"/>
+      <c r="P97" s="3"/>
+      <c r="Q97" s="3"/>
+      <c r="R97" s="3"/>
+    </row>
+    <row r="98" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G98" s="3"/>
+      <c r="H98" s="3"/>
+      <c r="I98" s="3"/>
+      <c r="J98" s="3"/>
+      <c r="K98" s="3"/>
+      <c r="L98" s="3"/>
+      <c r="M98" s="3"/>
+      <c r="N98" s="3"/>
+      <c r="O98" s="3"/>
+      <c r="P98" s="3"/>
+      <c r="Q98" s="3"/>
+      <c r="R98" s="3"/>
+    </row>
+    <row r="99" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G99" s="3"/>
+      <c r="H99" s="3"/>
+      <c r="I99" s="3"/>
+      <c r="J99" s="3"/>
+      <c r="K99" s="3"/>
+      <c r="L99" s="3"/>
+      <c r="M99" s="3"/>
+      <c r="N99" s="3"/>
+      <c r="O99" s="3"/>
+      <c r="P99" s="3"/>
+      <c r="Q99" s="3"/>
+      <c r="R99" s="3"/>
+    </row>
+    <row r="100" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G100" s="3"/>
+      <c r="H100" s="3"/>
+      <c r="I100" s="3"/>
+      <c r="J100" s="3"/>
+      <c r="K100" s="3"/>
+      <c r="L100" s="3"/>
+      <c r="M100" s="3"/>
+      <c r="N100" s="3"/>
+      <c r="O100" s="3"/>
+      <c r="P100" s="3"/>
+      <c r="Q100" s="3"/>
+      <c r="R100" s="3"/>
+    </row>
+    <row r="101" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G101" s="3"/>
+      <c r="H101" s="3"/>
+      <c r="I101" s="3"/>
+      <c r="J101" s="3"/>
+      <c r="K101" s="3"/>
+      <c r="L101" s="3"/>
+      <c r="M101" s="3"/>
+      <c r="N101" s="3"/>
+      <c r="O101" s="3"/>
+      <c r="P101" s="3"/>
+      <c r="Q101" s="3"/>
+      <c r="R101" s="3"/>
+    </row>
+    <row r="102" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G102" s="3"/>
+      <c r="H102" s="3"/>
+      <c r="I102" s="3"/>
+      <c r="J102" s="3"/>
+      <c r="K102" s="3"/>
+      <c r="L102" s="3"/>
+      <c r="M102" s="3"/>
+      <c r="N102" s="3"/>
+      <c r="O102" s="3"/>
+      <c r="P102" s="3"/>
+      <c r="Q102" s="3"/>
+      <c r="R102" s="3"/>
+    </row>
+    <row r="103" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G103" s="3"/>
+      <c r="H103" s="3"/>
+      <c r="I103" s="3"/>
+      <c r="J103" s="3"/>
+      <c r="K103" s="3"/>
+      <c r="L103" s="3"/>
+      <c r="M103" s="3"/>
+      <c r="N103" s="3"/>
+      <c r="O103" s="3"/>
+      <c r="P103" s="3"/>
+      <c r="Q103" s="3"/>
+      <c r="R103" s="3"/>
+    </row>
+    <row r="104" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G104" s="3"/>
+      <c r="H104" s="3"/>
+      <c r="I104" s="3"/>
+      <c r="J104" s="3"/>
+      <c r="K104" s="3"/>
+      <c r="L104" s="3"/>
+      <c r="M104" s="3"/>
+      <c r="N104" s="3"/>
+      <c r="O104" s="3"/>
+      <c r="P104" s="3"/>
+      <c r="Q104" s="3"/>
+      <c r="R104" s="3"/>
+    </row>
+    <row r="105" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G105" s="3"/>
+      <c r="H105" s="3"/>
+      <c r="I105" s="3"/>
+      <c r="J105" s="3"/>
+      <c r="K105" s="3"/>
+      <c r="L105" s="3"/>
+      <c r="M105" s="3"/>
+      <c r="N105" s="3"/>
+      <c r="O105" s="3"/>
+      <c r="P105" s="3"/>
+      <c r="Q105" s="3"/>
+      <c r="R105" s="3"/>
+    </row>
+    <row r="106" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G106" s="3"/>
+      <c r="H106" s="3"/>
+      <c r="I106" s="3"/>
+      <c r="J106" s="3"/>
+      <c r="K106" s="3"/>
+      <c r="L106" s="3"/>
+      <c r="M106" s="3"/>
+      <c r="N106" s="3"/>
+      <c r="O106" s="3"/>
+      <c r="P106" s="3"/>
+      <c r="Q106" s="3"/>
+      <c r="R106" s="3"/>
+    </row>
+    <row r="107" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G107" s="3"/>
+      <c r="H107" s="3"/>
+      <c r="I107" s="3"/>
+      <c r="J107" s="3"/>
+      <c r="K107" s="3"/>
+      <c r="L107" s="3"/>
+      <c r="M107" s="3"/>
+      <c r="N107" s="3"/>
+      <c r="O107" s="3"/>
+      <c r="P107" s="3"/>
+      <c r="Q107" s="3"/>
+      <c r="R107" s="3"/>
+    </row>
+    <row r="108" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G108" s="3"/>
+      <c r="H108" s="3"/>
+      <c r="I108" s="3"/>
+      <c r="J108" s="3"/>
+      <c r="K108" s="3"/>
+      <c r="L108" s="3"/>
+      <c r="M108" s="3"/>
+      <c r="N108" s="3"/>
+      <c r="O108" s="3"/>
+      <c r="P108" s="3"/>
+      <c r="Q108" s="3"/>
+      <c r="R108" s="3"/>
+    </row>
+    <row r="109" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G109" s="3"/>
+      <c r="H109" s="3"/>
+      <c r="I109" s="3"/>
+      <c r="J109" s="3"/>
+      <c r="K109" s="3"/>
+      <c r="L109" s="3"/>
+      <c r="M109" s="3"/>
+      <c r="N109" s="3"/>
+      <c r="O109" s="3"/>
+      <c r="P109" s="3"/>
+      <c r="Q109" s="3"/>
+      <c r="R109" s="3"/>
+    </row>
+    <row r="110" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G110" s="3"/>
+      <c r="H110" s="3"/>
+      <c r="I110" s="3"/>
+      <c r="J110" s="3"/>
+      <c r="K110" s="3"/>
+      <c r="L110" s="3"/>
+      <c r="M110" s="3"/>
+      <c r="N110" s="3"/>
+      <c r="O110" s="3"/>
+      <c r="P110" s="3"/>
+      <c r="Q110" s="3"/>
+      <c r="R110" s="3"/>
+    </row>
+    <row r="111" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G111" s="3"/>
+      <c r="H111" s="3"/>
+      <c r="I111" s="3"/>
+      <c r="J111" s="3"/>
+      <c r="K111" s="3"/>
+      <c r="L111" s="3"/>
+      <c r="M111" s="3"/>
+      <c r="N111" s="3"/>
+      <c r="O111" s="3"/>
+      <c r="P111" s="3"/>
+      <c r="Q111" s="3"/>
+      <c r="R111" s="3"/>
+    </row>
+    <row r="112" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G112" s="3"/>
+      <c r="H112" s="3"/>
+      <c r="I112" s="3"/>
+      <c r="J112" s="3"/>
+      <c r="K112" s="3"/>
+      <c r="L112" s="3"/>
+      <c r="M112" s="3"/>
+      <c r="N112" s="3"/>
+      <c r="O112" s="3"/>
+      <c r="P112" s="3"/>
+      <c r="Q112" s="3"/>
+      <c r="R112" s="3"/>
+    </row>
+    <row r="113" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G113" s="3"/>
+      <c r="H113" s="3"/>
+      <c r="I113" s="3"/>
+      <c r="J113" s="3"/>
+      <c r="K113" s="3"/>
+      <c r="L113" s="3"/>
+      <c r="M113" s="3"/>
+      <c r="N113" s="3"/>
+      <c r="O113" s="3"/>
+      <c r="P113" s="3"/>
+      <c r="Q113" s="3"/>
+      <c r="R113" s="3"/>
+    </row>
+    <row r="114" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G114" s="3"/>
+      <c r="H114" s="3"/>
+      <c r="I114" s="3"/>
+      <c r="J114" s="3"/>
+      <c r="K114" s="3"/>
+      <c r="L114" s="3"/>
+      <c r="M114" s="3"/>
+      <c r="N114" s="3"/>
+      <c r="O114" s="3"/>
+      <c r="P114" s="3"/>
+      <c r="Q114" s="3"/>
+      <c r="R114" s="3"/>
+    </row>
+    <row r="115" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G115" s="3"/>
+      <c r="H115" s="3"/>
+      <c r="I115" s="3"/>
+      <c r="J115" s="3"/>
+      <c r="K115" s="3"/>
+      <c r="L115" s="3"/>
+      <c r="M115" s="3"/>
+      <c r="N115" s="3"/>
+      <c r="O115" s="3"/>
+      <c r="P115" s="3"/>
+      <c r="Q115" s="3"/>
+      <c r="R115" s="3"/>
+    </row>
+    <row r="116" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G116" s="3"/>
+      <c r="H116" s="3"/>
+      <c r="I116" s="3"/>
+      <c r="J116" s="3"/>
+      <c r="K116" s="3"/>
+      <c r="L116" s="3"/>
+      <c r="M116" s="3"/>
+      <c r="N116" s="3"/>
+      <c r="O116" s="3"/>
+      <c r="P116" s="3"/>
+      <c r="Q116" s="3"/>
+      <c r="R116" s="3"/>
+    </row>
+    <row r="117" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G117" s="3"/>
+      <c r="H117" s="3"/>
+      <c r="I117" s="3"/>
+      <c r="J117" s="3"/>
+      <c r="K117" s="3"/>
+      <c r="L117" s="3"/>
+      <c r="M117" s="3"/>
+      <c r="N117" s="3"/>
+      <c r="O117" s="3"/>
+      <c r="P117" s="3"/>
+      <c r="Q117" s="3"/>
+      <c r="R117" s="3"/>
+    </row>
+    <row r="118" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G118" s="3"/>
+      <c r="H118" s="3"/>
+      <c r="I118" s="3"/>
+      <c r="J118" s="3"/>
+      <c r="K118" s="3"/>
+      <c r="L118" s="3"/>
+      <c r="M118" s="3"/>
+      <c r="N118" s="3"/>
+      <c r="O118" s="3"/>
+      <c r="P118" s="3"/>
+      <c r="Q118" s="3"/>
+      <c r="R118" s="3"/>
+    </row>
+    <row r="119" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G119" s="3"/>
+      <c r="H119" s="3"/>
+      <c r="I119" s="3"/>
+      <c r="J119" s="3"/>
+      <c r="K119" s="3"/>
+      <c r="L119" s="3"/>
+      <c r="M119" s="3"/>
+      <c r="N119" s="3"/>
+      <c r="O119" s="3"/>
+      <c r="P119" s="3"/>
+      <c r="Q119" s="3"/>
+      <c r="R119" s="3"/>
+    </row>
+    <row r="120" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G120" s="3"/>
+      <c r="H120" s="3"/>
+      <c r="I120" s="3"/>
+      <c r="J120" s="3"/>
+      <c r="K120" s="3"/>
+      <c r="L120" s="3"/>
+      <c r="M120" s="3"/>
+      <c r="N120" s="3"/>
+      <c r="O120" s="3"/>
+      <c r="P120" s="3"/>
+      <c r="Q120" s="3"/>
+      <c r="R120" s="3"/>
+    </row>
+    <row r="121" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G121" s="3"/>
+      <c r="H121" s="3"/>
+      <c r="I121" s="3"/>
+      <c r="J121" s="3"/>
+      <c r="K121" s="3"/>
+      <c r="L121" s="3"/>
+      <c r="M121" s="3"/>
+      <c r="N121" s="3"/>
+      <c r="O121" s="3"/>
+      <c r="P121" s="3"/>
+      <c r="Q121" s="3"/>
+      <c r="R121" s="3"/>
+    </row>
+    <row r="122" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G122" s="3"/>
+      <c r="H122" s="3"/>
+      <c r="I122" s="3"/>
+      <c r="J122" s="3"/>
+      <c r="K122" s="3"/>
+      <c r="L122" s="3"/>
+      <c r="M122" s="3"/>
+      <c r="N122" s="3"/>
+      <c r="O122" s="3"/>
+      <c r="P122" s="3"/>
+      <c r="Q122" s="3"/>
+      <c r="R122" s="3"/>
+    </row>
+    <row r="123" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G123" s="3"/>
+      <c r="H123" s="3"/>
+      <c r="I123" s="3"/>
+      <c r="J123" s="3"/>
+      <c r="K123" s="3"/>
+      <c r="L123" s="3"/>
+      <c r="M123" s="3"/>
+      <c r="N123" s="3"/>
+      <c r="O123" s="3"/>
+      <c r="P123" s="3"/>
+      <c r="Q123" s="3"/>
+      <c r="R123" s="3"/>
+    </row>
+    <row r="124" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G124" s="3"/>
+      <c r="H124" s="3"/>
+      <c r="I124" s="3"/>
+      <c r="J124" s="3"/>
+      <c r="K124" s="3"/>
+      <c r="L124" s="3"/>
+      <c r="M124" s="3"/>
+      <c r="N124" s="3"/>
+      <c r="O124" s="3"/>
+      <c r="P124" s="3"/>
+      <c r="Q124" s="3"/>
+      <c r="R124" s="3"/>
+    </row>
+    <row r="125" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G125" s="3"/>
+      <c r="H125" s="3"/>
+      <c r="I125" s="3"/>
+      <c r="J125" s="3"/>
+      <c r="K125" s="3"/>
+      <c r="L125" s="3"/>
+      <c r="M125" s="3"/>
+      <c r="N125" s="3"/>
+      <c r="O125" s="3"/>
+      <c r="P125" s="3"/>
+      <c r="Q125" s="3"/>
+      <c r="R125" s="3"/>
+    </row>
+    <row r="126" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G126" s="3"/>
+      <c r="H126" s="3"/>
+      <c r="I126" s="3"/>
+      <c r="J126" s="3"/>
+      <c r="K126" s="3"/>
+      <c r="L126" s="3"/>
+      <c r="M126" s="3"/>
+      <c r="N126" s="3"/>
+      <c r="O126" s="3"/>
+      <c r="P126" s="3"/>
+      <c r="Q126" s="3"/>
+      <c r="R126" s="3"/>
+    </row>
+    <row r="127" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G127" s="3"/>
+      <c r="H127" s="3"/>
+      <c r="I127" s="3"/>
+      <c r="J127" s="3"/>
+      <c r="K127" s="3"/>
+      <c r="L127" s="3"/>
+      <c r="M127" s="3"/>
+      <c r="N127" s="3"/>
+      <c r="O127" s="3"/>
+      <c r="P127" s="3"/>
+      <c r="Q127" s="3"/>
+      <c r="R127" s="3"/>
+    </row>
+    <row r="128" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G128" s="3"/>
+      <c r="H128" s="3"/>
+      <c r="I128" s="3"/>
+      <c r="J128" s="3"/>
+      <c r="K128" s="3"/>
+      <c r="L128" s="3"/>
+      <c r="M128" s="3"/>
+      <c r="N128" s="3"/>
+      <c r="O128" s="3"/>
+      <c r="P128" s="3"/>
+      <c r="Q128" s="3"/>
+      <c r="R128" s="3"/>
+    </row>
+    <row r="129" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G129" s="3"/>
+      <c r="H129" s="3"/>
+      <c r="I129" s="3"/>
+      <c r="J129" s="3"/>
+      <c r="K129" s="3"/>
+      <c r="L129" s="3"/>
+      <c r="M129" s="3"/>
+      <c r="N129" s="3"/>
+      <c r="O129" s="3"/>
+      <c r="P129" s="3"/>
+      <c r="Q129" s="3"/>
+      <c r="R129" s="3"/>
+    </row>
+    <row r="130" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G130" s="3"/>
+      <c r="H130" s="3"/>
+      <c r="I130" s="3"/>
+      <c r="J130" s="3"/>
+      <c r="K130" s="3"/>
+      <c r="L130" s="3"/>
+      <c r="M130" s="3"/>
+      <c r="N130" s="3"/>
+      <c r="O130" s="3"/>
+      <c r="P130" s="3"/>
+      <c r="Q130" s="3"/>
+      <c r="R130" s="3"/>
+    </row>
+    <row r="131" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G131" s="3"/>
+      <c r="H131" s="3"/>
+      <c r="I131" s="3"/>
+      <c r="J131" s="3"/>
+      <c r="K131" s="3"/>
+      <c r="L131" s="3"/>
+      <c r="M131" s="3"/>
+      <c r="N131" s="3"/>
+      <c r="O131" s="3"/>
+      <c r="P131" s="3"/>
+      <c r="Q131" s="3"/>
+      <c r="R131" s="3"/>
+    </row>
+    <row r="132" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G132" s="3"/>
+      <c r="H132" s="3"/>
+      <c r="I132" s="3"/>
+      <c r="J132" s="3"/>
+      <c r="K132" s="3"/>
+      <c r="L132" s="3"/>
+      <c r="M132" s="3"/>
+      <c r="N132" s="3"/>
+      <c r="O132" s="3"/>
+      <c r="P132" s="3"/>
+      <c r="Q132" s="3"/>
+      <c r="R132" s="3"/>
+    </row>
+    <row r="133" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G133" s="3"/>
+      <c r="H133" s="3"/>
+      <c r="I133" s="3"/>
+      <c r="J133" s="3"/>
+      <c r="K133" s="3"/>
+      <c r="L133" s="3"/>
+      <c r="M133" s="3"/>
+      <c r="N133" s="3"/>
+      <c r="O133" s="3"/>
+      <c r="P133" s="3"/>
+      <c r="Q133" s="3"/>
+      <c r="R133" s="3"/>
+    </row>
+    <row r="134" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G134" s="3"/>
+      <c r="H134" s="3"/>
+      <c r="I134" s="3"/>
+      <c r="J134" s="3"/>
+      <c r="K134" s="3"/>
+      <c r="L134" s="3"/>
+      <c r="M134" s="3"/>
+      <c r="N134" s="3"/>
+      <c r="O134" s="3"/>
+      <c r="P134" s="3"/>
+      <c r="Q134" s="3"/>
+      <c r="R134" s="3"/>
+    </row>
+    <row r="135" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G135" s="3"/>
+      <c r="H135" s="3"/>
+      <c r="I135" s="3"/>
+      <c r="J135" s="3"/>
+      <c r="K135" s="3"/>
+      <c r="L135" s="3"/>
+      <c r="M135" s="3"/>
+      <c r="N135" s="3"/>
+      <c r="O135" s="3"/>
+      <c r="P135" s="3"/>
+      <c r="Q135" s="3"/>
+      <c r="R135" s="3"/>
+    </row>
+    <row r="136" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G136" s="3"/>
+      <c r="H136" s="3"/>
+      <c r="I136" s="3"/>
+      <c r="J136" s="3"/>
+      <c r="K136" s="3"/>
+      <c r="L136" s="3"/>
+      <c r="M136" s="3"/>
+      <c r="N136" s="3"/>
+      <c r="O136" s="3"/>
+      <c r="P136" s="3"/>
+      <c r="Q136" s="3"/>
+      <c r="R136" s="3"/>
+    </row>
+    <row r="137" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G137" s="3"/>
+      <c r="H137" s="3"/>
+      <c r="I137" s="3"/>
+      <c r="J137" s="3"/>
+      <c r="K137" s="3"/>
+      <c r="L137" s="3"/>
+      <c r="M137" s="3"/>
+      <c r="N137" s="3"/>
+      <c r="O137" s="3"/>
+      <c r="P137" s="3"/>
+      <c r="Q137" s="3"/>
+      <c r="R137" s="3"/>
+    </row>
+    <row r="138" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G138" s="3"/>
+      <c r="H138" s="3"/>
+      <c r="I138" s="3"/>
+      <c r="J138" s="3"/>
+      <c r="K138" s="3"/>
+      <c r="L138" s="3"/>
+      <c r="M138" s="3"/>
+      <c r="N138" s="3"/>
+      <c r="O138" s="3"/>
+      <c r="P138" s="3"/>
+      <c r="Q138" s="3"/>
+      <c r="R138" s="3"/>
+    </row>
+    <row r="139" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G139" s="3"/>
+      <c r="H139" s="3"/>
+      <c r="I139" s="3"/>
+      <c r="J139" s="3"/>
+      <c r="K139" s="3"/>
+      <c r="L139" s="3"/>
+      <c r="M139" s="3"/>
+      <c r="N139" s="3"/>
+      <c r="O139" s="3"/>
+      <c r="P139" s="3"/>
+      <c r="Q139" s="3"/>
+      <c r="R139" s="3"/>
+    </row>
+    <row r="140" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G140" s="3"/>
+      <c r="H140" s="3"/>
+      <c r="I140" s="3"/>
+      <c r="J140" s="3"/>
+      <c r="K140" s="3"/>
+      <c r="L140" s="3"/>
+      <c r="M140" s="3"/>
+      <c r="N140" s="3"/>
+      <c r="O140" s="3"/>
+      <c r="P140" s="3"/>
+      <c r="Q140" s="3"/>
+      <c r="R140" s="3"/>
+    </row>
+    <row r="141" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G141" s="3"/>
+      <c r="H141" s="3"/>
+      <c r="I141" s="3"/>
+      <c r="J141" s="3"/>
+      <c r="K141" s="3"/>
+      <c r="L141" s="3"/>
+      <c r="M141" s="3"/>
+      <c r="N141" s="3"/>
+      <c r="O141" s="3"/>
+      <c r="P141" s="3"/>
+      <c r="Q141" s="3"/>
+      <c r="R141" s="3"/>
+    </row>
+    <row r="142" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G142" s="3"/>
+      <c r="H142" s="3"/>
+      <c r="I142" s="3"/>
+      <c r="J142" s="3"/>
+      <c r="K142" s="3"/>
+      <c r="L142" s="3"/>
+      <c r="M142" s="3"/>
+      <c r="N142" s="3"/>
+      <c r="O142" s="3"/>
+      <c r="P142" s="3"/>
+      <c r="Q142" s="3"/>
+      <c r="R142" s="3"/>
+    </row>
+    <row r="143" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G143" s="3"/>
+      <c r="H143" s="3"/>
+      <c r="I143" s="3"/>
+      <c r="J143" s="3"/>
+      <c r="K143" s="3"/>
+      <c r="L143" s="3"/>
+      <c r="M143" s="3"/>
+      <c r="N143" s="3"/>
+      <c r="O143" s="3"/>
+      <c r="P143" s="3"/>
+      <c r="Q143" s="3"/>
+      <c r="R143" s="3"/>
+    </row>
+    <row r="144" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G144" s="3"/>
+      <c r="H144" s="3"/>
+      <c r="I144" s="3"/>
+      <c r="J144" s="3"/>
+      <c r="K144" s="3"/>
+      <c r="L144" s="3"/>
+      <c r="M144" s="3"/>
+      <c r="N144" s="3"/>
+      <c r="O144" s="3"/>
+      <c r="P144" s="3"/>
+      <c r="Q144" s="3"/>
+      <c r="R144" s="3"/>
+    </row>
+    <row r="145" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G145" s="3"/>
+      <c r="H145" s="3"/>
+      <c r="I145" s="3"/>
+      <c r="J145" s="3"/>
+      <c r="K145" s="3"/>
+      <c r="L145" s="3"/>
+      <c r="M145" s="3"/>
+      <c r="N145" s="3"/>
+      <c r="O145" s="3"/>
+      <c r="P145" s="3"/>
+      <c r="Q145" s="3"/>
+      <c r="R145" s="3"/>
+    </row>
+    <row r="146" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G146" s="3"/>
+      <c r="H146" s="3"/>
+      <c r="I146" s="3"/>
+      <c r="J146" s="3"/>
+      <c r="K146" s="3"/>
+      <c r="L146" s="3"/>
+      <c r="M146" s="3"/>
+      <c r="N146" s="3"/>
+      <c r="O146" s="3"/>
+      <c r="P146" s="3"/>
+      <c r="Q146" s="3"/>
+      <c r="R146" s="3"/>
+    </row>
+    <row r="147" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G147" s="3"/>
+      <c r="H147" s="3"/>
+      <c r="I147" s="3"/>
+      <c r="J147" s="3"/>
+      <c r="K147" s="3"/>
+      <c r="L147" s="3"/>
+      <c r="M147" s="3"/>
+      <c r="N147" s="3"/>
+      <c r="O147" s="3"/>
+      <c r="P147" s="3"/>
+      <c r="Q147" s="3"/>
+      <c r="R147" s="3"/>
+    </row>
+    <row r="148" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G148" s="3"/>
+      <c r="H148" s="3"/>
+      <c r="I148" s="3"/>
+      <c r="J148" s="3"/>
+      <c r="K148" s="3"/>
+      <c r="L148" s="3"/>
+      <c r="M148" s="3"/>
+      <c r="N148" s="3"/>
+      <c r="O148" s="3"/>
+      <c r="P148" s="3"/>
+      <c r="Q148" s="3"/>
+      <c r="R148" s="3"/>
+    </row>
+    <row r="149" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G149" s="3"/>
+      <c r="H149" s="3"/>
+      <c r="I149" s="3"/>
+      <c r="J149" s="3"/>
+      <c r="K149" s="3"/>
+      <c r="L149" s="3"/>
+      <c r="M149" s="3"/>
+      <c r="N149" s="3"/>
+      <c r="O149" s="3"/>
+      <c r="P149" s="3"/>
+      <c r="Q149" s="3"/>
+      <c r="R149" s="3"/>
+    </row>
+    <row r="150" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G150" s="3"/>
+      <c r="H150" s="3"/>
+      <c r="I150" s="3"/>
+      <c r="J150" s="3"/>
+      <c r="K150" s="3"/>
+      <c r="L150" s="3"/>
+      <c r="M150" s="3"/>
+      <c r="N150" s="3"/>
+      <c r="O150" s="3"/>
+      <c r="P150" s="3"/>
+      <c r="Q150" s="3"/>
+      <c r="R150" s="3"/>
+    </row>
+    <row r="151" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G151" s="3"/>
+      <c r="H151" s="3"/>
+      <c r="I151" s="3"/>
+      <c r="J151" s="3"/>
+      <c r="K151" s="3"/>
+      <c r="L151" s="3"/>
+      <c r="M151" s="3"/>
+      <c r="N151" s="3"/>
+      <c r="O151" s="3"/>
+      <c r="P151" s="3"/>
+      <c r="Q151" s="3"/>
+      <c r="R151" s="3"/>
+    </row>
+    <row r="152" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G152" s="3"/>
+      <c r="H152" s="3"/>
+      <c r="I152" s="3"/>
+      <c r="J152" s="3"/>
+      <c r="K152" s="3"/>
+      <c r="L152" s="3"/>
+      <c r="M152" s="3"/>
+      <c r="N152" s="3"/>
+      <c r="O152" s="3"/>
+      <c r="P152" s="3"/>
+      <c r="Q152" s="3"/>
+      <c r="R152" s="3"/>
+    </row>
+    <row r="153" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G153" s="3"/>
+      <c r="H153" s="3"/>
+      <c r="I153" s="3"/>
+      <c r="J153" s="3"/>
+      <c r="K153" s="3"/>
+      <c r="L153" s="3"/>
+      <c r="M153" s="3"/>
+      <c r="N153" s="3"/>
+      <c r="O153" s="3"/>
+      <c r="P153" s="3"/>
+      <c r="Q153" s="3"/>
+      <c r="R153" s="3"/>
+    </row>
+    <row r="154" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G154" s="3"/>
+      <c r="H154" s="3"/>
+      <c r="I154" s="3"/>
+      <c r="J154" s="3"/>
+      <c r="K154" s="3"/>
+      <c r="L154" s="3"/>
+      <c r="M154" s="3"/>
+      <c r="N154" s="3"/>
+      <c r="O154" s="3"/>
+      <c r="P154" s="3"/>
+      <c r="Q154" s="3"/>
+      <c r="R154" s="3"/>
+    </row>
+    <row r="155" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G155" s="3"/>
+      <c r="H155" s="3"/>
+      <c r="I155" s="3"/>
+      <c r="J155" s="3"/>
+      <c r="K155" s="3"/>
+      <c r="L155" s="3"/>
+      <c r="M155" s="3"/>
+      <c r="N155" s="3"/>
+      <c r="O155" s="3"/>
+      <c r="P155" s="3"/>
+      <c r="Q155" s="3"/>
+      <c r="R155" s="3"/>
+    </row>
+    <row r="156" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G156" s="3"/>
+      <c r="H156" s="3"/>
+      <c r="I156" s="3"/>
+      <c r="J156" s="3"/>
+      <c r="K156" s="3"/>
+      <c r="L156" s="3"/>
+      <c r="M156" s="3"/>
+      <c r="N156" s="3"/>
+      <c r="O156" s="3"/>
+      <c r="P156" s="3"/>
+      <c r="Q156" s="3"/>
+      <c r="R156" s="3"/>
+    </row>
+    <row r="157" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G157" s="3"/>
+      <c r="H157" s="3"/>
+      <c r="I157" s="3"/>
+      <c r="J157" s="3"/>
+      <c r="K157" s="3"/>
+      <c r="L157" s="3"/>
+      <c r="M157" s="3"/>
+      <c r="N157" s="3"/>
+      <c r="O157" s="3"/>
+      <c r="P157" s="3"/>
+      <c r="Q157" s="3"/>
+      <c r="R157" s="3"/>
+    </row>
+    <row r="158" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G158" s="3"/>
+      <c r="H158" s="3"/>
+      <c r="I158" s="3"/>
+      <c r="J158" s="3"/>
+      <c r="K158" s="3"/>
+      <c r="L158" s="3"/>
+      <c r="M158" s="3"/>
+      <c r="N158" s="3"/>
+      <c r="O158" s="3"/>
+      <c r="P158" s="3"/>
+      <c r="Q158" s="3"/>
+      <c r="R158" s="3"/>
+    </row>
+    <row r="159" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G159" s="3"/>
+      <c r="H159" s="3"/>
+      <c r="I159" s="3"/>
+      <c r="J159" s="3"/>
+      <c r="K159" s="3"/>
+      <c r="L159" s="3"/>
+      <c r="M159" s="3"/>
+      <c r="N159" s="3"/>
+      <c r="O159" s="3"/>
+      <c r="P159" s="3"/>
+      <c r="Q159" s="3"/>
+      <c r="R159" s="3"/>
+    </row>
+    <row r="160" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G160" s="3"/>
+      <c r="H160" s="3"/>
+      <c r="I160" s="3"/>
+      <c r="J160" s="3"/>
+      <c r="K160" s="3"/>
+      <c r="L160" s="3"/>
+      <c r="M160" s="3"/>
+      <c r="N160" s="3"/>
+      <c r="O160" s="3"/>
+      <c r="P160" s="3"/>
+      <c r="Q160" s="3"/>
+      <c r="R160" s="3"/>
+    </row>
+    <row r="161" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G161" s="3"/>
+      <c r="H161" s="3"/>
+      <c r="I161" s="3"/>
+      <c r="J161" s="3"/>
+      <c r="K161" s="3"/>
+      <c r="L161" s="3"/>
+      <c r="M161" s="3"/>
+      <c r="N161" s="3"/>
+      <c r="O161" s="3"/>
+      <c r="P161" s="3"/>
+      <c r="Q161" s="3"/>
+      <c r="R161" s="3"/>
+    </row>
+    <row r="162" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G162" s="3"/>
+      <c r="H162" s="3"/>
+      <c r="I162" s="3"/>
+      <c r="J162" s="3"/>
+      <c r="K162" s="3"/>
+      <c r="L162" s="3"/>
+      <c r="M162" s="3"/>
+      <c r="N162" s="3"/>
+      <c r="O162" s="3"/>
+      <c r="P162" s="3"/>
+      <c r="Q162" s="3"/>
+      <c r="R162" s="3"/>
+    </row>
+    <row r="163" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G163" s="3"/>
+      <c r="H163" s="3"/>
+      <c r="I163" s="3"/>
+      <c r="J163" s="3"/>
+      <c r="K163" s="3"/>
+      <c r="L163" s="3"/>
+      <c r="M163" s="3"/>
+      <c r="N163" s="3"/>
+      <c r="O163" s="3"/>
+      <c r="P163" s="3"/>
+      <c r="Q163" s="3"/>
+      <c r="R163" s="3"/>
+    </row>
+    <row r="164" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G164" s="3"/>
+      <c r="H164" s="3"/>
+      <c r="I164" s="3"/>
+      <c r="J164" s="3"/>
+      <c r="K164" s="3"/>
+      <c r="L164" s="3"/>
+      <c r="M164" s="3"/>
+      <c r="N164" s="3"/>
+      <c r="O164" s="3"/>
+      <c r="P164" s="3"/>
+      <c r="Q164" s="3"/>
+      <c r="R164" s="3"/>
+    </row>
+    <row r="165" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G165" s="3"/>
+      <c r="H165" s="3"/>
+      <c r="I165" s="3"/>
+      <c r="J165" s="3"/>
+      <c r="K165" s="3"/>
+      <c r="L165" s="3"/>
+      <c r="M165" s="3"/>
+      <c r="N165" s="3"/>
+      <c r="O165" s="3"/>
+      <c r="P165" s="3"/>
+      <c r="Q165" s="3"/>
+      <c r="R165" s="3"/>
+    </row>
+    <row r="166" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G166" s="3"/>
+      <c r="H166" s="3"/>
+      <c r="I166" s="3"/>
+      <c r="J166" s="3"/>
+      <c r="K166" s="3"/>
+      <c r="L166" s="3"/>
+      <c r="M166" s="3"/>
+      <c r="N166" s="3"/>
+      <c r="O166" s="3"/>
+      <c r="P166" s="3"/>
+      <c r="Q166" s="3"/>
+      <c r="R166" s="3"/>
+    </row>
+    <row r="167" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G167" s="3"/>
+      <c r="H167" s="3"/>
+      <c r="I167" s="3"/>
+      <c r="J167" s="3"/>
+      <c r="K167" s="3"/>
+      <c r="L167" s="3"/>
+      <c r="M167" s="3"/>
+      <c r="N167" s="3"/>
+      <c r="O167" s="3"/>
+      <c r="P167" s="3"/>
+      <c r="Q167" s="3"/>
+      <c r="R167" s="3"/>
+    </row>
+    <row r="168" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G168" s="3"/>
+      <c r="H168" s="3"/>
+      <c r="I168" s="3"/>
+      <c r="J168" s="3"/>
+      <c r="K168" s="3"/>
+      <c r="L168" s="3"/>
+      <c r="M168" s="3"/>
+      <c r="N168" s="3"/>
+      <c r="O168" s="3"/>
+      <c r="P168" s="3"/>
+      <c r="Q168" s="3"/>
+      <c r="R168" s="3"/>
+    </row>
+    <row r="169" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G169" s="3"/>
+      <c r="H169" s="3"/>
+      <c r="I169" s="3"/>
+      <c r="J169" s="3"/>
+      <c r="K169" s="3"/>
+      <c r="L169" s="3"/>
+      <c r="M169" s="3"/>
+      <c r="N169" s="3"/>
+      <c r="O169" s="3"/>
+      <c r="P169" s="3"/>
+      <c r="Q169" s="3"/>
+      <c r="R169" s="3"/>
+    </row>
+    <row r="170" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G170" s="3"/>
+      <c r="H170" s="3"/>
+      <c r="I170" s="3"/>
+      <c r="J170" s="3"/>
+      <c r="K170" s="3"/>
+      <c r="L170" s="3"/>
+      <c r="M170" s="3"/>
+      <c r="N170" s="3"/>
+      <c r="O170" s="3"/>
+      <c r="P170" s="3"/>
+      <c r="Q170" s="3"/>
+      <c r="R170" s="3"/>
+    </row>
+    <row r="171" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G171" s="3"/>
+      <c r="H171" s="3"/>
+      <c r="I171" s="3"/>
+      <c r="J171" s="3"/>
+      <c r="K171" s="3"/>
+      <c r="L171" s="3"/>
+      <c r="M171" s="3"/>
+      <c r="N171" s="3"/>
+      <c r="O171" s="3"/>
+      <c r="P171" s="3"/>
+      <c r="Q171" s="3"/>
+      <c r="R171" s="3"/>
+    </row>
+    <row r="172" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G172" s="3"/>
+      <c r="H172" s="3"/>
+      <c r="I172" s="3"/>
+      <c r="J172" s="3"/>
+      <c r="K172" s="3"/>
+      <c r="L172" s="3"/>
+      <c r="M172" s="3"/>
+      <c r="N172" s="3"/>
+      <c r="O172" s="3"/>
+      <c r="P172" s="3"/>
+      <c r="Q172" s="3"/>
+      <c r="R172" s="3"/>
+    </row>
+    <row r="173" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G173" s="3"/>
+      <c r="H173" s="3"/>
+      <c r="I173" s="3"/>
+      <c r="J173" s="3"/>
+      <c r="K173" s="3"/>
+      <c r="L173" s="3"/>
+      <c r="M173" s="3"/>
+      <c r="N173" s="3"/>
+      <c r="O173" s="3"/>
+      <c r="P173" s="3"/>
+      <c r="Q173" s="3"/>
+      <c r="R173" s="3"/>
+    </row>
+    <row r="174" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G174" s="3"/>
+      <c r="H174" s="3"/>
+      <c r="I174" s="3"/>
+      <c r="J174" s="3"/>
+      <c r="K174" s="3"/>
+      <c r="L174" s="3"/>
+      <c r="M174" s="3"/>
+      <c r="N174" s="3"/>
+      <c r="O174" s="3"/>
+      <c r="P174" s="3"/>
+      <c r="Q174" s="3"/>
+      <c r="R174" s="3"/>
+    </row>
+    <row r="175" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G175" s="3"/>
+      <c r="H175" s="3"/>
+      <c r="I175" s="3"/>
+      <c r="J175" s="3"/>
+      <c r="K175" s="3"/>
+      <c r="L175" s="3"/>
+      <c r="M175" s="3"/>
+      <c r="N175" s="3"/>
+      <c r="O175" s="3"/>
+      <c r="P175" s="3"/>
+      <c r="Q175" s="3"/>
+      <c r="R175" s="3"/>
+    </row>
+    <row r="176" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G176" s="3"/>
+      <c r="H176" s="3"/>
+      <c r="I176" s="3"/>
+      <c r="J176" s="3"/>
+      <c r="K176" s="3"/>
+      <c r="L176" s="3"/>
+      <c r="M176" s="3"/>
+      <c r="N176" s="3"/>
+      <c r="O176" s="3"/>
+      <c r="P176" s="3"/>
+      <c r="Q176" s="3"/>
+      <c r="R176" s="3"/>
+    </row>
+    <row r="177" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G177" s="3"/>
+      <c r="H177" s="3"/>
+      <c r="I177" s="3"/>
+      <c r="J177" s="3"/>
+      <c r="K177" s="3"/>
+      <c r="L177" s="3"/>
+      <c r="M177" s="3"/>
+      <c r="N177" s="3"/>
+      <c r="O177" s="3"/>
+      <c r="P177" s="3"/>
+      <c r="Q177" s="3"/>
+      <c r="R177" s="3"/>
+    </row>
+    <row r="178" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G178" s="3"/>
+      <c r="H178" s="3"/>
+      <c r="I178" s="3"/>
+      <c r="J178" s="3"/>
+      <c r="K178" s="3"/>
+      <c r="L178" s="3"/>
+      <c r="M178" s="3"/>
+      <c r="N178" s="3"/>
+      <c r="O178" s="3"/>
+      <c r="P178" s="3"/>
+      <c r="Q178" s="3"/>
+      <c r="R178" s="3"/>
+    </row>
+    <row r="179" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G179" s="3"/>
+      <c r="H179" s="3"/>
+      <c r="I179" s="3"/>
+      <c r="J179" s="3"/>
+      <c r="K179" s="3"/>
+      <c r="L179" s="3"/>
+      <c r="M179" s="3"/>
+      <c r="N179" s="3"/>
+      <c r="O179" s="3"/>
+      <c r="P179" s="3"/>
+      <c r="Q179" s="3"/>
+      <c r="R179" s="3"/>
+    </row>
+    <row r="180" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G180" s="3"/>
+      <c r="H180" s="3"/>
+      <c r="I180" s="3"/>
+      <c r="J180" s="3"/>
+      <c r="K180" s="3"/>
+      <c r="L180" s="3"/>
+      <c r="M180" s="3"/>
+      <c r="N180" s="3"/>
+      <c r="O180" s="3"/>
+      <c r="P180" s="3"/>
+      <c r="Q180" s="3"/>
+      <c r="R180" s="3"/>
+    </row>
+    <row r="181" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G181" s="3"/>
+      <c r="H181" s="3"/>
+      <c r="I181" s="3"/>
+      <c r="J181" s="3"/>
+      <c r="K181" s="3"/>
+      <c r="L181" s="3"/>
+      <c r="M181" s="3"/>
+      <c r="N181" s="3"/>
+      <c r="O181" s="3"/>
+      <c r="P181" s="3"/>
+      <c r="Q181" s="3"/>
+      <c r="R181" s="3"/>
+    </row>
+    <row r="182" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G182" s="3"/>
+      <c r="H182" s="3"/>
+      <c r="I182" s="3"/>
+      <c r="J182" s="3"/>
+      <c r="K182" s="3"/>
+      <c r="L182" s="3"/>
+      <c r="M182" s="3"/>
+      <c r="N182" s="3"/>
+      <c r="O182" s="3"/>
+      <c r="P182" s="3"/>
+      <c r="Q182" s="3"/>
+      <c r="R182" s="3"/>
+    </row>
+    <row r="183" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G183" s="3"/>
+      <c r="H183" s="3"/>
+      <c r="I183" s="3"/>
+      <c r="J183" s="3"/>
+      <c r="K183" s="3"/>
+      <c r="L183" s="3"/>
+      <c r="M183" s="3"/>
+      <c r="N183" s="3"/>
+      <c r="O183" s="3"/>
+      <c r="P183" s="3"/>
+      <c r="Q183" s="3"/>
+      <c r="R183" s="3"/>
+    </row>
+    <row r="184" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G184" s="3"/>
+      <c r="H184" s="3"/>
+      <c r="I184" s="3"/>
+      <c r="J184" s="3"/>
+      <c r="K184" s="3"/>
+      <c r="L184" s="3"/>
+      <c r="M184" s="3"/>
+      <c r="N184" s="3"/>
+      <c r="O184" s="3"/>
+      <c r="P184" s="3"/>
+      <c r="Q184" s="3"/>
+      <c r="R184" s="3"/>
+    </row>
+    <row r="185" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G185" s="3"/>
+      <c r="H185" s="3"/>
+      <c r="I185" s="3"/>
+      <c r="J185" s="3"/>
+      <c r="K185" s="3"/>
+      <c r="L185" s="3"/>
+      <c r="M185" s="3"/>
+      <c r="N185" s="3"/>
+      <c r="O185" s="3"/>
+      <c r="P185" s="3"/>
+      <c r="Q185" s="3"/>
+      <c r="R185" s="3"/>
+    </row>
+    <row r="186" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G186" s="3"/>
+      <c r="H186" s="3"/>
+      <c r="I186" s="3"/>
+      <c r="J186" s="3"/>
+      <c r="K186" s="3"/>
+      <c r="L186" s="3"/>
+      <c r="M186" s="3"/>
+      <c r="N186" s="3"/>
+      <c r="O186" s="3"/>
+      <c r="P186" s="3"/>
+      <c r="Q186" s="3"/>
+      <c r="R186" s="3"/>
+    </row>
+    <row r="187" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G187" s="3"/>
+      <c r="H187" s="3"/>
+      <c r="I187" s="3"/>
+      <c r="J187" s="3"/>
+      <c r="K187" s="3"/>
+      <c r="L187" s="3"/>
+      <c r="M187" s="3"/>
+      <c r="N187" s="3"/>
+      <c r="O187" s="3"/>
+      <c r="P187" s="3"/>
+      <c r="Q187" s="3"/>
+      <c r="R187" s="3"/>
+    </row>
+    <row r="188" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G188" s="3"/>
+      <c r="H188" s="3"/>
+      <c r="I188" s="3"/>
+      <c r="J188" s="3"/>
+      <c r="K188" s="3"/>
+      <c r="L188" s="3"/>
+      <c r="M188" s="3"/>
+      <c r="N188" s="3"/>
+      <c r="O188" s="3"/>
+      <c r="P188" s="3"/>
+      <c r="Q188" s="3"/>
+      <c r="R188" s="3"/>
+    </row>
+    <row r="189" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G189" s="3"/>
+      <c r="H189" s="3"/>
+      <c r="I189" s="3"/>
+      <c r="J189" s="3"/>
+      <c r="K189" s="3"/>
+      <c r="L189" s="3"/>
+      <c r="M189" s="3"/>
+      <c r="N189" s="3"/>
+      <c r="O189" s="3"/>
+      <c r="P189" s="3"/>
+      <c r="Q189" s="3"/>
+      <c r="R189" s="3"/>
+    </row>
+    <row r="190" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G190" s="3"/>
+      <c r="H190" s="3"/>
+      <c r="I190" s="3"/>
+      <c r="J190" s="3"/>
+      <c r="K190" s="3"/>
+      <c r="L190" s="3"/>
+      <c r="M190" s="3"/>
+      <c r="N190" s="3"/>
+      <c r="O190" s="3"/>
+      <c r="P190" s="3"/>
+      <c r="Q190" s="3"/>
+      <c r="R190" s="3"/>
+    </row>
+    <row r="191" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G191" s="3"/>
+      <c r="H191" s="3"/>
+      <c r="I191" s="3"/>
+      <c r="J191" s="3"/>
+      <c r="K191" s="3"/>
+      <c r="L191" s="3"/>
+      <c r="M191" s="3"/>
+      <c r="N191" s="3"/>
+      <c r="O191" s="3"/>
+      <c r="P191" s="3"/>
+      <c r="Q191" s="3"/>
+      <c r="R191" s="3"/>
+    </row>
+    <row r="192" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G192" s="3"/>
+      <c r="H192" s="3"/>
+      <c r="I192" s="3"/>
+      <c r="J192" s="3"/>
+      <c r="K192" s="3"/>
+      <c r="L192" s="3"/>
+      <c r="M192" s="3"/>
+      <c r="N192" s="3"/>
+      <c r="O192" s="3"/>
+      <c r="P192" s="3"/>
+      <c r="Q192" s="3"/>
+      <c r="R192" s="3"/>
+    </row>
+    <row r="193" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G193" s="3"/>
+      <c r="H193" s="3"/>
+      <c r="I193" s="3"/>
+      <c r="J193" s="3"/>
+      <c r="K193" s="3"/>
+      <c r="L193" s="3"/>
+      <c r="M193" s="3"/>
+      <c r="N193" s="3"/>
+      <c r="O193" s="3"/>
+      <c r="P193" s="3"/>
+      <c r="Q193" s="3"/>
+      <c r="R193" s="3"/>
+    </row>
+    <row r="194" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G194" s="3"/>
+      <c r="H194" s="3"/>
+      <c r="I194" s="3"/>
+      <c r="J194" s="3"/>
+      <c r="K194" s="3"/>
+      <c r="L194" s="3"/>
+      <c r="M194" s="3"/>
+      <c r="N194" s="3"/>
+      <c r="O194" s="3"/>
+      <c r="P194" s="3"/>
+      <c r="Q194" s="3"/>
+      <c r="R194" s="3"/>
+    </row>
+    <row r="195" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G195" s="3"/>
+      <c r="H195" s="3"/>
+      <c r="I195" s="3"/>
+      <c r="J195" s="3"/>
+      <c r="K195" s="3"/>
+      <c r="L195" s="3"/>
+      <c r="M195" s="3"/>
+      <c r="N195" s="3"/>
+      <c r="O195" s="3"/>
+      <c r="P195" s="3"/>
+      <c r="Q195" s="3"/>
+      <c r="R195" s="3"/>
+    </row>
+    <row r="196" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G196" s="3"/>
+      <c r="H196" s="3"/>
+      <c r="I196" s="3"/>
+      <c r="J196" s="3"/>
+      <c r="K196" s="3"/>
+      <c r="L196" s="3"/>
+      <c r="M196" s="3"/>
+      <c r="N196" s="3"/>
+      <c r="O196" s="3"/>
+      <c r="P196" s="3"/>
+      <c r="Q196" s="3"/>
+      <c r="R196" s="3"/>
+    </row>
+    <row r="197" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G197" s="3"/>
+      <c r="H197" s="3"/>
+      <c r="I197" s="3"/>
+      <c r="J197" s="3"/>
+      <c r="K197" s="3"/>
+      <c r="L197" s="3"/>
+      <c r="M197" s="3"/>
+      <c r="N197" s="3"/>
+      <c r="O197" s="3"/>
+      <c r="P197" s="3"/>
+      <c r="Q197" s="3"/>
+      <c r="R197" s="3"/>
+    </row>
+    <row r="198" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G198" s="3"/>
+      <c r="H198" s="3"/>
+      <c r="I198" s="3"/>
+      <c r="J198" s="3"/>
+      <c r="K198" s="3"/>
+      <c r="L198" s="3"/>
+      <c r="M198" s="3"/>
+      <c r="N198" s="3"/>
+      <c r="O198" s="3"/>
+      <c r="P198" s="3"/>
+      <c r="Q198" s="3"/>
+      <c r="R198" s="3"/>
+    </row>
+    <row r="199" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G199" s="3"/>
+      <c r="H199" s="3"/>
+      <c r="I199" s="3"/>
+      <c r="J199" s="3"/>
+      <c r="K199" s="3"/>
+      <c r="L199" s="3"/>
+      <c r="M199" s="3"/>
+      <c r="N199" s="3"/>
+      <c r="O199" s="3"/>
+      <c r="P199" s="3"/>
+      <c r="Q199" s="3"/>
+      <c r="R199" s="3"/>
+    </row>
+    <row r="200" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G200" s="3"/>
+      <c r="H200" s="3"/>
+      <c r="I200" s="3"/>
+      <c r="J200" s="3"/>
+      <c r="K200" s="3"/>
+      <c r="L200" s="3"/>
+      <c r="M200" s="3"/>
+      <c r="N200" s="3"/>
+      <c r="O200" s="3"/>
+      <c r="P200" s="3"/>
+      <c r="Q200" s="3"/>
+      <c r="R200" s="3"/>
+    </row>
+    <row r="201" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G201" s="3"/>
+      <c r="H201" s="3"/>
+      <c r="I201" s="3"/>
+      <c r="J201" s="3"/>
+      <c r="K201" s="3"/>
+      <c r="L201" s="3"/>
+      <c r="M201" s="3"/>
+      <c r="N201" s="3"/>
+      <c r="O201" s="3"/>
+      <c r="P201" s="3"/>
+      <c r="Q201" s="3"/>
+      <c r="R201" s="3"/>
+    </row>
+    <row r="202" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G202" s="3"/>
+      <c r="H202" s="3"/>
+      <c r="I202" s="3"/>
+      <c r="J202" s="3"/>
+      <c r="K202" s="3"/>
+      <c r="L202" s="3"/>
+      <c r="M202" s="3"/>
+      <c r="N202" s="3"/>
+      <c r="O202" s="3"/>
+      <c r="P202" s="3"/>
+      <c r="Q202" s="3"/>
+      <c r="R202" s="3"/>
+    </row>
+    <row r="203" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G203" s="3"/>
+      <c r="H203" s="3"/>
+      <c r="I203" s="3"/>
+      <c r="J203" s="3"/>
+      <c r="K203" s="3"/>
+      <c r="L203" s="3"/>
+      <c r="M203" s="3"/>
+      <c r="N203" s="3"/>
+      <c r="O203" s="3"/>
+      <c r="P203" s="3"/>
+      <c r="Q203" s="3"/>
+      <c r="R203" s="3"/>
+    </row>
+    <row r="204" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G204" s="3"/>
+      <c r="H204" s="3"/>
+      <c r="I204" s="3"/>
+      <c r="J204" s="3"/>
+      <c r="K204" s="3"/>
+      <c r="L204" s="3"/>
+      <c r="M204" s="3"/>
+      <c r="N204" s="3"/>
+      <c r="O204" s="3"/>
+      <c r="P204" s="3"/>
+      <c r="Q204" s="3"/>
+      <c r="R204" s="3"/>
+    </row>
+    <row r="205" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G205" s="3"/>
+      <c r="H205" s="3"/>
+      <c r="I205" s="3"/>
+      <c r="J205" s="3"/>
+      <c r="K205" s="3"/>
+      <c r="L205" s="3"/>
+      <c r="M205" s="3"/>
+      <c r="N205" s="3"/>
+      <c r="O205" s="3"/>
+      <c r="P205" s="3"/>
+      <c r="Q205" s="3"/>
+      <c r="R205" s="3"/>
+    </row>
+    <row r="206" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G206" s="3"/>
+      <c r="H206" s="3"/>
+      <c r="I206" s="3"/>
+      <c r="J206" s="3"/>
+      <c r="K206" s="3"/>
+      <c r="L206" s="3"/>
+      <c r="M206" s="3"/>
+      <c r="N206" s="3"/>
+      <c r="O206" s="3"/>
+      <c r="P206" s="3"/>
+      <c r="Q206" s="3"/>
+      <c r="R206" s="3"/>
+    </row>
+    <row r="207" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G207" s="3"/>
+      <c r="H207" s="3"/>
+      <c r="I207" s="3"/>
+      <c r="J207" s="3"/>
+      <c r="K207" s="3"/>
+      <c r="L207" s="3"/>
+      <c r="M207" s="3"/>
+      <c r="N207" s="3"/>
+      <c r="O207" s="3"/>
+      <c r="P207" s="3"/>
+      <c r="Q207" s="3"/>
+      <c r="R207" s="3"/>
+    </row>
+    <row r="208" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G208" s="3"/>
+      <c r="H208" s="3"/>
+      <c r="I208" s="3"/>
+      <c r="J208" s="3"/>
+      <c r="K208" s="3"/>
+      <c r="L208" s="3"/>
+      <c r="M208" s="3"/>
+      <c r="N208" s="3"/>
+      <c r="O208" s="3"/>
+      <c r="P208" s="3"/>
+      <c r="Q208" s="3"/>
+      <c r="R208" s="3"/>
+    </row>
+    <row r="209" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G209" s="3"/>
+      <c r="H209" s="3"/>
+      <c r="I209" s="3"/>
+      <c r="J209" s="3"/>
+      <c r="K209" s="3"/>
+      <c r="L209" s="3"/>
+      <c r="M209" s="3"/>
+      <c r="N209" s="3"/>
+      <c r="O209" s="3"/>
+      <c r="P209" s="3"/>
+      <c r="Q209" s="3"/>
+      <c r="R209" s="3"/>
+    </row>
+    <row r="210" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G210" s="3"/>
+      <c r="H210" s="3"/>
+      <c r="I210" s="3"/>
+      <c r="J210" s="3"/>
+      <c r="K210" s="3"/>
+      <c r="L210" s="3"/>
+      <c r="M210" s="3"/>
+      <c r="N210" s="3"/>
+      <c r="O210" s="3"/>
+      <c r="P210" s="3"/>
+      <c r="Q210" s="3"/>
+      <c r="R210" s="3"/>
+    </row>
+    <row r="211" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G211" s="3"/>
+      <c r="H211" s="3"/>
+      <c r="I211" s="3"/>
+      <c r="J211" s="3"/>
+      <c r="K211" s="3"/>
+      <c r="L211" s="3"/>
+      <c r="M211" s="3"/>
+      <c r="N211" s="3"/>
+      <c r="O211" s="3"/>
+      <c r="P211" s="3"/>
+      <c r="Q211" s="3"/>
+      <c r="R211" s="3"/>
+    </row>
+    <row r="212" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G212" s="3"/>
+      <c r="H212" s="3"/>
+      <c r="I212" s="3"/>
+      <c r="J212" s="3"/>
+      <c r="K212" s="3"/>
+      <c r="L212" s="3"/>
+      <c r="M212" s="3"/>
+      <c r="N212" s="3"/>
+      <c r="O212" s="3"/>
+      <c r="P212" s="3"/>
+      <c r="Q212" s="3"/>
+      <c r="R212" s="3"/>
+    </row>
+    <row r="213" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G213" s="3"/>
+      <c r="H213" s="3"/>
+      <c r="I213" s="3"/>
+      <c r="J213" s="3"/>
+      <c r="K213" s="3"/>
+      <c r="L213" s="3"/>
+      <c r="M213" s="3"/>
+      <c r="N213" s="3"/>
+      <c r="O213" s="3"/>
+      <c r="P213" s="3"/>
+      <c r="Q213" s="3"/>
+      <c r="R213" s="3"/>
+    </row>
+    <row r="214" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G214" s="3"/>
+      <c r="H214" s="3"/>
+      <c r="I214" s="3"/>
+      <c r="J214" s="3"/>
+      <c r="K214" s="3"/>
+      <c r="L214" s="3"/>
+      <c r="M214" s="3"/>
+      <c r="N214" s="3"/>
+      <c r="O214" s="3"/>
+      <c r="P214" s="3"/>
+      <c r="Q214" s="3"/>
+      <c r="R214" s="3"/>
+    </row>
+    <row r="215" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G215" s="3"/>
+      <c r="H215" s="3"/>
+      <c r="I215" s="3"/>
+      <c r="J215" s="3"/>
+      <c r="K215" s="3"/>
+      <c r="L215" s="3"/>
+      <c r="M215" s="3"/>
+      <c r="N215" s="3"/>
+      <c r="O215" s="3"/>
+      <c r="P215" s="3"/>
+      <c r="Q215" s="3"/>
+      <c r="R215" s="3"/>
+    </row>
+    <row r="216" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G216" s="3"/>
+      <c r="H216" s="3"/>
+      <c r="I216" s="3"/>
+      <c r="J216" s="3"/>
+      <c r="K216" s="3"/>
+      <c r="L216" s="3"/>
+      <c r="M216" s="3"/>
+      <c r="N216" s="3"/>
+      <c r="O216" s="3"/>
+      <c r="P216" s="3"/>
+      <c r="Q216" s="3"/>
+      <c r="R216" s="3"/>
+    </row>
+    <row r="217" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G217" s="3"/>
+      <c r="H217" s="3"/>
+      <c r="I217" s="3"/>
+      <c r="J217" s="3"/>
+      <c r="K217" s="3"/>
+      <c r="L217" s="3"/>
+      <c r="M217" s="3"/>
+      <c r="N217" s="3"/>
+      <c r="O217" s="3"/>
+      <c r="P217" s="3"/>
+      <c r="Q217" s="3"/>
+      <c r="R217" s="3"/>
+    </row>
+    <row r="218" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G218" s="3"/>
+      <c r="H218" s="3"/>
+      <c r="I218" s="3"/>
+      <c r="J218" s="3"/>
+      <c r="K218" s="3"/>
+      <c r="L218" s="3"/>
+      <c r="M218" s="3"/>
+      <c r="N218" s="3"/>
+      <c r="O218" s="3"/>
+      <c r="P218" s="3"/>
+      <c r="Q218" s="3"/>
+      <c r="R218" s="3"/>
+    </row>
+    <row r="219" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G219" s="3"/>
+      <c r="H219" s="3"/>
+      <c r="I219" s="3"/>
+      <c r="J219" s="3"/>
+      <c r="K219" s="3"/>
+      <c r="L219" s="3"/>
+      <c r="M219" s="3"/>
+      <c r="N219" s="3"/>
+      <c r="O219" s="3"/>
+      <c r="P219" s="3"/>
+      <c r="Q219" s="3"/>
+      <c r="R219" s="3"/>
+    </row>
+    <row r="220" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G220" s="3"/>
+      <c r="H220" s="3"/>
+      <c r="I220" s="3"/>
+      <c r="J220" s="3"/>
+      <c r="K220" s="3"/>
+      <c r="L220" s="3"/>
+      <c r="M220" s="3"/>
+      <c r="N220" s="3"/>
+      <c r="O220" s="3"/>
+      <c r="P220" s="3"/>
+      <c r="Q220" s="3"/>
+      <c r="R220" s="3"/>
+    </row>
+    <row r="221" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G221" s="3"/>
+      <c r="H221" s="3"/>
+      <c r="I221" s="3"/>
+      <c r="J221" s="3"/>
+      <c r="K221" s="3"/>
+      <c r="L221" s="3"/>
+      <c r="M221" s="3"/>
+      <c r="N221" s="3"/>
+      <c r="O221" s="3"/>
+      <c r="P221" s="3"/>
+      <c r="Q221" s="3"/>
+      <c r="R221" s="3"/>
+    </row>
+    <row r="222" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G222" s="3"/>
+      <c r="H222" s="3"/>
+      <c r="I222" s="3"/>
+      <c r="J222" s="3"/>
+      <c r="K222" s="3"/>
+      <c r="L222" s="3"/>
+      <c r="M222" s="3"/>
+      <c r="N222" s="3"/>
+      <c r="O222" s="3"/>
+      <c r="P222" s="3"/>
+      <c r="Q222" s="3"/>
+      <c r="R222" s="3"/>
+    </row>
+    <row r="223" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G223" s="3"/>
+      <c r="H223" s="3"/>
+      <c r="I223" s="3"/>
+      <c r="J223" s="3"/>
+      <c r="K223" s="3"/>
+      <c r="L223" s="3"/>
+      <c r="M223" s="3"/>
+      <c r="N223" s="3"/>
+      <c r="O223" s="3"/>
+      <c r="P223" s="3"/>
+      <c r="Q223" s="3"/>
+      <c r="R223" s="3"/>
+    </row>
+    <row r="224" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G224" s="3"/>
+      <c r="H224" s="3"/>
+      <c r="I224" s="3"/>
+      <c r="J224" s="3"/>
+      <c r="K224" s="3"/>
+      <c r="L224" s="3"/>
+      <c r="M224" s="3"/>
+      <c r="N224" s="3"/>
+      <c r="O224" s="3"/>
+      <c r="P224" s="3"/>
+      <c r="Q224" s="3"/>
+      <c r="R224" s="3"/>
+    </row>
+    <row r="225" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G225" s="3"/>
+      <c r="H225" s="3"/>
+      <c r="I225" s="3"/>
+      <c r="J225" s="3"/>
+      <c r="K225" s="3"/>
+      <c r="L225" s="3"/>
+      <c r="M225" s="3"/>
+      <c r="N225" s="3"/>
+      <c r="O225" s="3"/>
+      <c r="P225" s="3"/>
+      <c r="Q225" s="3"/>
+      <c r="R225" s="3"/>
+    </row>
+    <row r="226" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G226" s="3"/>
+      <c r="H226" s="3"/>
+      <c r="I226" s="3"/>
+      <c r="J226" s="3"/>
+      <c r="K226" s="3"/>
+      <c r="L226" s="3"/>
+      <c r="M226" s="3"/>
+      <c r="N226" s="3"/>
+      <c r="O226" s="3"/>
+      <c r="P226" s="3"/>
+      <c r="Q226" s="3"/>
+      <c r="R226" s="3"/>
+    </row>
+    <row r="227" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G227" s="3"/>
+      <c r="H227" s="3"/>
+      <c r="I227" s="3"/>
+      <c r="J227" s="3"/>
+      <c r="K227" s="3"/>
+      <c r="L227" s="3"/>
+      <c r="M227" s="3"/>
+      <c r="N227" s="3"/>
+      <c r="O227" s="3"/>
+      <c r="P227" s="3"/>
+      <c r="Q227" s="3"/>
+      <c r="R227" s="3"/>
+    </row>
+    <row r="228" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G228" s="3"/>
+      <c r="H228" s="3"/>
+      <c r="I228" s="3"/>
+      <c r="J228" s="3"/>
+      <c r="K228" s="3"/>
+      <c r="L228" s="3"/>
+      <c r="M228" s="3"/>
+      <c r="N228" s="3"/>
+      <c r="O228" s="3"/>
+      <c r="P228" s="3"/>
+      <c r="Q228" s="3"/>
+      <c r="R228" s="3"/>
+    </row>
+    <row r="229" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G229" s="3"/>
+      <c r="H229" s="3"/>
+      <c r="I229" s="3"/>
+      <c r="J229" s="3"/>
+      <c r="K229" s="3"/>
+      <c r="L229" s="3"/>
+      <c r="M229" s="3"/>
+      <c r="N229" s="3"/>
+      <c r="O229" s="3"/>
+      <c r="P229" s="3"/>
+      <c r="Q229" s="3"/>
+      <c r="R229" s="3"/>
+    </row>
+    <row r="230" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G230" s="3"/>
+      <c r="H230" s="3"/>
+      <c r="I230" s="3"/>
+      <c r="J230" s="3"/>
+      <c r="K230" s="3"/>
+      <c r="L230" s="3"/>
+      <c r="M230" s="3"/>
+      <c r="N230" s="3"/>
+      <c r="O230" s="3"/>
+      <c r="P230" s="3"/>
+      <c r="Q230" s="3"/>
+      <c r="R230" s="3"/>
+    </row>
+    <row r="231" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G231" s="3"/>
+      <c r="H231" s="3"/>
+      <c r="I231" s="3"/>
+      <c r="J231" s="3"/>
+      <c r="K231" s="3"/>
+      <c r="L231" s="3"/>
+      <c r="M231" s="3"/>
+      <c r="N231" s="3"/>
+      <c r="O231" s="3"/>
+      <c r="P231" s="3"/>
+      <c r="Q231" s="3"/>
+      <c r="R231" s="3"/>
+    </row>
+    <row r="232" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G232" s="3"/>
+      <c r="H232" s="3"/>
+      <c r="I232" s="3"/>
+      <c r="J232" s="3"/>
+      <c r="K232" s="3"/>
+      <c r="L232" s="3"/>
+      <c r="M232" s="3"/>
+      <c r="N232" s="3"/>
+      <c r="O232" s="3"/>
+      <c r="P232" s="3"/>
+      <c r="Q232" s="3"/>
+      <c r="R232" s="3"/>
+    </row>
+    <row r="233" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G233" s="3"/>
+      <c r="H233" s="3"/>
+      <c r="I233" s="3"/>
+      <c r="J233" s="3"/>
+      <c r="K233" s="3"/>
+      <c r="L233" s="3"/>
+      <c r="M233" s="3"/>
+      <c r="N233" s="3"/>
+      <c r="O233" s="3"/>
+      <c r="P233" s="3"/>
+      <c r="Q233" s="3"/>
+      <c r="R233" s="3"/>
+    </row>
+    <row r="234" spans="7:18" x14ac:dyDescent="0.25">
+      <c r="G234" s="3"/>
+      <c r="H234" s="3"/>
+      <c r="I234" s="3"/>
+      <c r="J234" s="3"/>
+      <c r="K234" s="3"/>
+      <c r="L234" s="3"/>
+      <c r="M234" s="3"/>
+      <c r="N234" s="3"/>
+      <c r="O234" s="3"/>
+      <c r="P234" s="3"/>
+      <c r="Q234" s="3"/>
+      <c r="R234" s="3"/>
+    </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>